--- a/public/sample/users_import.xlsx
+++ b/public/sample/users_import.xlsx
@@ -1,17 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pc\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48269766-7475-418E-BDD6-602B941DF30E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>SRNO</t>
   </si>
@@ -73,111 +82,28 @@
     <t>Zone</t>
   </si>
   <si>
-    <t>demo12@gmail.com</t>
+    <t>Region</t>
   </si>
   <si>
-    <t>Hello</t>
+    <t>Branch</t>
   </si>
   <si>
-    <t>World</t>
-  </si>
-  <si>
-    <t>EMP001</t>
-  </si>
-  <si>
-    <t>Lko</t>
-  </si>
-  <si>
-    <t>India</t>
-  </si>
-  <si>
-    <t>Uttar Pradesh</t>
-  </si>
-  <si>
-    <t>Noida</t>
-  </si>
-  <si>
-    <t>Active</t>
-  </si>
-  <si>
-    <t>Developer</t>
-  </si>
-  <si>
-    <t>Part 1</t>
-  </si>
-  <si>
-    <t>Hybrid</t>
-  </si>
-  <si>
-    <t>Zone 1</t>
-  </si>
-  <si>
-    <t>demo2@gmail.com</t>
-  </si>
-  <si>
-    <t>Hello 1</t>
-  </si>
-  <si>
-    <t>World 1</t>
-  </si>
-  <si>
-    <t>EMP002</t>
-  </si>
-  <si>
-    <t>Lucknow</t>
-  </si>
-  <si>
-    <t>Part 2</t>
-  </si>
-  <si>
-    <t>Full time</t>
-  </si>
-  <si>
-    <t>Zone 2</t>
-  </si>
-  <si>
-    <t>demo3@gmail.com</t>
-  </si>
-  <si>
-    <t>Hello 2</t>
-  </si>
-  <si>
-    <t>World 2</t>
-  </si>
-  <si>
-    <t>EMP003</t>
-  </si>
-  <si>
-    <t>Ghazipur</t>
-  </si>
-  <si>
-    <t>Inactive</t>
-  </si>
-  <si>
-    <t>Salesforce Developer</t>
-  </si>
-  <si>
-    <t>Part 3</t>
-  </si>
-  <si>
-    <t>Part time</t>
-  </si>
-  <si>
-    <t>Zone 3</t>
+    <t>Department</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -188,37 +114,44 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -408,17 +341,45 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:W1000"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="10.5703125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -479,4186 +440,4075 @@
       <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="1">
-        <v>9.450300233E9</v>
-      </c>
-      <c r="F2" s="1">
-        <v>9.450300232E9</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="L2" s="1">
-        <v>123456.0</v>
-      </c>
-      <c r="M2" s="1">
-        <v>1.23456789E8</v>
-      </c>
-      <c r="N2" s="1">
-        <v>1.23456789E8</v>
-      </c>
-      <c r="O2" s="1">
-        <v>1.23456789E8</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E3" s="1">
-        <v>9.450300231E9</v>
-      </c>
-      <c r="F3" s="1">
-        <v>9.450300233E9</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="L3" s="1">
-        <v>123456.0</v>
-      </c>
-      <c r="M3" s="1">
-        <v>1.23456789E8</v>
-      </c>
-      <c r="N3" s="1">
-        <v>1.23456789E8</v>
-      </c>
-      <c r="O3" s="1">
-        <v>1.23456789E8</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="S3" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="T3" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1">
-        <v>4.0</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E4" s="1">
-        <v>9.450300232E9</v>
-      </c>
-      <c r="F4" s="1">
-        <v>9.450300234E9</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="L4" s="1">
-        <v>123456.0</v>
-      </c>
-      <c r="M4" s="1">
-        <v>1.23456789E8</v>
-      </c>
-      <c r="N4" s="1">
-        <v>1.23456789E8</v>
-      </c>
-      <c r="O4" s="1">
-        <v>1.23456789E8</v>
-      </c>
-      <c r="P4" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q4" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="R4" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="S4" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="T4" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="5">
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="1"/>
+      <c r="O3" s="1"/>
+      <c r="P3" s="1"/>
+      <c r="Q3" s="1"/>
+      <c r="R3" s="1"/>
+      <c r="S3" s="1"/>
+      <c r="T3" s="1"/>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
+      <c r="P4" s="1"/>
+      <c r="Q4" s="1"/>
+      <c r="R4" s="1"/>
+      <c r="S4" s="1"/>
+      <c r="T4" s="1"/>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="P5" s="2"/>
       <c r="S5" s="2"/>
     </row>
-    <row r="6">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="P6" s="2"/>
       <c r="S6" s="2"/>
     </row>
-    <row r="7">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="P7" s="2"/>
       <c r="S7" s="2"/>
     </row>
-    <row r="8">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="P8" s="2"/>
       <c r="S8" s="2"/>
     </row>
-    <row r="9">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="P9" s="2"/>
       <c r="S9" s="2"/>
     </row>
-    <row r="10">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="P10" s="2"/>
       <c r="S10" s="2"/>
     </row>
-    <row r="11">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="P11" s="2"/>
       <c r="S11" s="2"/>
     </row>
-    <row r="12">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="P12" s="2"/>
       <c r="S12" s="2"/>
     </row>
-    <row r="13">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="P13" s="1"/>
       <c r="S13" s="2"/>
     </row>
-    <row r="14">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="P14" s="2"/>
       <c r="S14" s="2"/>
     </row>
-    <row r="15">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="P15" s="2"/>
       <c r="S15" s="2"/>
     </row>
-    <row r="16">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="P16" s="2"/>
       <c r="S16" s="2"/>
     </row>
-    <row r="17">
+    <row r="17" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P17" s="2"/>
       <c r="S17" s="2"/>
     </row>
-    <row r="18">
+    <row r="18" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P18" s="2"/>
       <c r="S18" s="2"/>
     </row>
-    <row r="19">
+    <row r="19" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P19" s="2"/>
       <c r="S19" s="2"/>
     </row>
-    <row r="20">
+    <row r="20" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P20" s="2"/>
       <c r="S20" s="2"/>
     </row>
-    <row r="21">
+    <row r="21" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P21" s="2"/>
       <c r="S21" s="2"/>
     </row>
-    <row r="22">
+    <row r="22" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P22" s="2"/>
       <c r="S22" s="2"/>
     </row>
-    <row r="23">
+    <row r="23" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P23" s="2"/>
       <c r="S23" s="2"/>
     </row>
-    <row r="24">
+    <row r="24" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P24" s="2"/>
       <c r="S24" s="2"/>
     </row>
-    <row r="25">
+    <row r="25" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P25" s="2"/>
       <c r="S25" s="2"/>
     </row>
-    <row r="26">
+    <row r="26" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P26" s="2"/>
       <c r="S26" s="2"/>
     </row>
-    <row r="27">
+    <row r="27" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P27" s="2"/>
       <c r="S27" s="2"/>
     </row>
-    <row r="28">
+    <row r="28" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P28" s="2"/>
       <c r="S28" s="2"/>
     </row>
-    <row r="29">
+    <row r="29" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P29" s="2"/>
       <c r="S29" s="2"/>
     </row>
-    <row r="30">
+    <row r="30" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P30" s="2"/>
       <c r="S30" s="2"/>
     </row>
-    <row r="31">
+    <row r="31" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P31" s="2"/>
       <c r="S31" s="2"/>
     </row>
-    <row r="32">
+    <row r="32" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P32" s="2"/>
       <c r="S32" s="2"/>
     </row>
-    <row r="33">
+    <row r="33" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P33" s="2"/>
       <c r="S33" s="2"/>
     </row>
-    <row r="34">
+    <row r="34" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P34" s="2"/>
       <c r="S34" s="2"/>
     </row>
-    <row r="35">
+    <row r="35" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P35" s="2"/>
       <c r="S35" s="2"/>
     </row>
-    <row r="36">
+    <row r="36" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P36" s="2"/>
       <c r="S36" s="2"/>
     </row>
-    <row r="37">
+    <row r="37" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P37" s="2"/>
       <c r="S37" s="2"/>
     </row>
-    <row r="38">
+    <row r="38" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P38" s="2"/>
       <c r="S38" s="2"/>
     </row>
-    <row r="39">
+    <row r="39" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P39" s="2"/>
       <c r="S39" s="2"/>
     </row>
-    <row r="40">
+    <row r="40" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P40" s="2"/>
       <c r="S40" s="2"/>
     </row>
-    <row r="41">
+    <row r="41" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P41" s="2"/>
       <c r="S41" s="2"/>
     </row>
-    <row r="42">
+    <row r="42" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P42" s="2"/>
       <c r="S42" s="2"/>
     </row>
-    <row r="43">
+    <row r="43" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P43" s="2"/>
       <c r="S43" s="2"/>
     </row>
-    <row r="44">
+    <row r="44" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P44" s="2"/>
       <c r="S44" s="2"/>
     </row>
-    <row r="45">
+    <row r="45" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P45" s="2"/>
       <c r="S45" s="2"/>
     </row>
-    <row r="46">
+    <row r="46" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P46" s="2"/>
       <c r="S46" s="2"/>
     </row>
-    <row r="47">
+    <row r="47" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P47" s="2"/>
       <c r="S47" s="2"/>
     </row>
-    <row r="48">
+    <row r="48" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P48" s="2"/>
       <c r="S48" s="2"/>
     </row>
-    <row r="49">
+    <row r="49" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P49" s="2"/>
       <c r="S49" s="2"/>
     </row>
-    <row r="50">
+    <row r="50" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P50" s="2"/>
       <c r="S50" s="2"/>
     </row>
-    <row r="51">
+    <row r="51" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P51" s="2"/>
       <c r="S51" s="2"/>
     </row>
-    <row r="52">
+    <row r="52" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P52" s="2"/>
       <c r="S52" s="2"/>
     </row>
-    <row r="53">
+    <row r="53" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P53" s="2"/>
       <c r="S53" s="2"/>
     </row>
-    <row r="54">
+    <row r="54" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P54" s="2"/>
       <c r="S54" s="2"/>
     </row>
-    <row r="55">
+    <row r="55" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P55" s="2"/>
       <c r="S55" s="2"/>
     </row>
-    <row r="56">
+    <row r="56" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P56" s="2"/>
       <c r="S56" s="2"/>
     </row>
-    <row r="57">
+    <row r="57" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P57" s="2"/>
       <c r="S57" s="2"/>
     </row>
-    <row r="58">
+    <row r="58" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P58" s="2"/>
       <c r="S58" s="2"/>
     </row>
-    <row r="59">
+    <row r="59" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P59" s="2"/>
       <c r="S59" s="2"/>
     </row>
-    <row r="60">
+    <row r="60" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P60" s="2"/>
       <c r="S60" s="2"/>
     </row>
-    <row r="61">
+    <row r="61" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P61" s="2"/>
       <c r="S61" s="2"/>
     </row>
-    <row r="62">
+    <row r="62" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P62" s="2"/>
       <c r="S62" s="2"/>
     </row>
-    <row r="63">
+    <row r="63" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P63" s="2"/>
       <c r="S63" s="2"/>
     </row>
-    <row r="64">
+    <row r="64" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P64" s="2"/>
       <c r="S64" s="2"/>
     </row>
-    <row r="65">
+    <row r="65" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P65" s="2"/>
       <c r="S65" s="2"/>
     </row>
-    <row r="66">
+    <row r="66" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P66" s="2"/>
       <c r="S66" s="2"/>
     </row>
-    <row r="67">
+    <row r="67" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P67" s="2"/>
       <c r="S67" s="2"/>
     </row>
-    <row r="68">
+    <row r="68" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P68" s="2"/>
       <c r="S68" s="2"/>
     </row>
-    <row r="69">
+    <row r="69" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P69" s="2"/>
       <c r="S69" s="2"/>
     </row>
-    <row r="70">
+    <row r="70" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P70" s="2"/>
       <c r="S70" s="2"/>
     </row>
-    <row r="71">
+    <row r="71" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P71" s="2"/>
       <c r="S71" s="2"/>
     </row>
-    <row r="72">
+    <row r="72" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P72" s="2"/>
       <c r="S72" s="2"/>
     </row>
-    <row r="73">
+    <row r="73" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P73" s="2"/>
       <c r="S73" s="2"/>
     </row>
-    <row r="74">
+    <row r="74" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P74" s="2"/>
       <c r="S74" s="2"/>
     </row>
-    <row r="75">
+    <row r="75" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P75" s="2"/>
       <c r="S75" s="2"/>
     </row>
-    <row r="76">
+    <row r="76" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P76" s="2"/>
       <c r="S76" s="2"/>
     </row>
-    <row r="77">
+    <row r="77" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P77" s="2"/>
       <c r="S77" s="2"/>
     </row>
-    <row r="78">
+    <row r="78" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P78" s="2"/>
       <c r="S78" s="2"/>
     </row>
-    <row r="79">
+    <row r="79" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P79" s="2"/>
       <c r="S79" s="2"/>
     </row>
-    <row r="80">
+    <row r="80" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P80" s="2"/>
       <c r="S80" s="2"/>
     </row>
-    <row r="81">
+    <row r="81" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P81" s="2"/>
       <c r="S81" s="2"/>
     </row>
-    <row r="82">
+    <row r="82" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P82" s="2"/>
       <c r="S82" s="2"/>
     </row>
-    <row r="83">
+    <row r="83" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P83" s="2"/>
       <c r="S83" s="2"/>
     </row>
-    <row r="84">
+    <row r="84" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P84" s="2"/>
       <c r="S84" s="2"/>
     </row>
-    <row r="85">
+    <row r="85" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P85" s="2"/>
       <c r="S85" s="2"/>
     </row>
-    <row r="86">
+    <row r="86" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P86" s="2"/>
       <c r="S86" s="2"/>
     </row>
-    <row r="87">
+    <row r="87" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P87" s="2"/>
       <c r="S87" s="2"/>
     </row>
-    <row r="88">
+    <row r="88" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P88" s="2"/>
       <c r="S88" s="2"/>
     </row>
-    <row r="89">
+    <row r="89" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P89" s="2"/>
       <c r="S89" s="2"/>
     </row>
-    <row r="90">
+    <row r="90" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P90" s="2"/>
       <c r="S90" s="2"/>
     </row>
-    <row r="91">
+    <row r="91" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P91" s="2"/>
       <c r="S91" s="2"/>
     </row>
-    <row r="92">
+    <row r="92" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P92" s="2"/>
       <c r="S92" s="2"/>
     </row>
-    <row r="93">
+    <row r="93" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P93" s="2"/>
       <c r="S93" s="2"/>
     </row>
-    <row r="94">
+    <row r="94" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P94" s="2"/>
       <c r="S94" s="2"/>
     </row>
-    <row r="95">
+    <row r="95" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P95" s="2"/>
       <c r="S95" s="2"/>
     </row>
-    <row r="96">
+    <row r="96" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P96" s="2"/>
       <c r="S96" s="2"/>
     </row>
-    <row r="97">
+    <row r="97" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P97" s="2"/>
       <c r="S97" s="2"/>
     </row>
-    <row r="98">
+    <row r="98" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P98" s="2"/>
       <c r="S98" s="2"/>
     </row>
-    <row r="99">
+    <row r="99" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P99" s="2"/>
       <c r="S99" s="2"/>
     </row>
-    <row r="100">
+    <row r="100" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P100" s="2"/>
       <c r="S100" s="2"/>
     </row>
-    <row r="101">
+    <row r="101" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P101" s="2"/>
       <c r="S101" s="2"/>
     </row>
-    <row r="102">
+    <row r="102" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P102" s="2"/>
       <c r="S102" s="2"/>
     </row>
-    <row r="103">
+    <row r="103" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P103" s="2"/>
       <c r="S103" s="2"/>
     </row>
-    <row r="104">
+    <row r="104" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P104" s="2"/>
       <c r="S104" s="2"/>
     </row>
-    <row r="105">
+    <row r="105" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P105" s="2"/>
       <c r="S105" s="2"/>
     </row>
-    <row r="106">
+    <row r="106" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P106" s="2"/>
       <c r="S106" s="2"/>
     </row>
-    <row r="107">
+    <row r="107" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P107" s="2"/>
       <c r="S107" s="2"/>
     </row>
-    <row r="108">
+    <row r="108" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P108" s="2"/>
       <c r="S108" s="2"/>
     </row>
-    <row r="109">
+    <row r="109" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P109" s="2"/>
       <c r="S109" s="2"/>
     </row>
-    <row r="110">
+    <row r="110" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P110" s="2"/>
       <c r="S110" s="2"/>
     </row>
-    <row r="111">
+    <row r="111" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P111" s="2"/>
       <c r="S111" s="2"/>
     </row>
-    <row r="112">
+    <row r="112" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P112" s="2"/>
       <c r="S112" s="2"/>
     </row>
-    <row r="113">
+    <row r="113" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P113" s="2"/>
       <c r="S113" s="2"/>
     </row>
-    <row r="114">
+    <row r="114" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P114" s="2"/>
       <c r="S114" s="2"/>
     </row>
-    <row r="115">
+    <row r="115" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P115" s="2"/>
       <c r="S115" s="2"/>
     </row>
-    <row r="116">
+    <row r="116" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P116" s="2"/>
       <c r="S116" s="2"/>
     </row>
-    <row r="117">
+    <row r="117" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P117" s="2"/>
       <c r="S117" s="2"/>
     </row>
-    <row r="118">
+    <row r="118" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P118" s="2"/>
       <c r="S118" s="2"/>
     </row>
-    <row r="119">
+    <row r="119" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P119" s="2"/>
       <c r="S119" s="2"/>
     </row>
-    <row r="120">
+    <row r="120" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P120" s="2"/>
       <c r="S120" s="2"/>
     </row>
-    <row r="121">
+    <row r="121" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P121" s="2"/>
       <c r="S121" s="2"/>
     </row>
-    <row r="122">
+    <row r="122" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P122" s="2"/>
       <c r="S122" s="2"/>
     </row>
-    <row r="123">
+    <row r="123" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P123" s="2"/>
       <c r="S123" s="2"/>
     </row>
-    <row r="124">
+    <row r="124" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P124" s="2"/>
       <c r="S124" s="2"/>
     </row>
-    <row r="125">
+    <row r="125" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P125" s="2"/>
       <c r="S125" s="2"/>
     </row>
-    <row r="126">
+    <row r="126" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P126" s="2"/>
       <c r="S126" s="2"/>
     </row>
-    <row r="127">
+    <row r="127" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P127" s="2"/>
       <c r="S127" s="2"/>
     </row>
-    <row r="128">
+    <row r="128" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P128" s="2"/>
       <c r="S128" s="2"/>
     </row>
-    <row r="129">
+    <row r="129" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P129" s="2"/>
       <c r="S129" s="2"/>
     </row>
-    <row r="130">
+    <row r="130" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P130" s="2"/>
       <c r="S130" s="2"/>
     </row>
-    <row r="131">
+    <row r="131" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P131" s="2"/>
       <c r="S131" s="2"/>
     </row>
-    <row r="132">
+    <row r="132" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P132" s="2"/>
       <c r="S132" s="2"/>
     </row>
-    <row r="133">
+    <row r="133" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P133" s="2"/>
       <c r="S133" s="2"/>
     </row>
-    <row r="134">
+    <row r="134" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P134" s="2"/>
       <c r="S134" s="2"/>
     </row>
-    <row r="135">
+    <row r="135" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P135" s="2"/>
       <c r="S135" s="2"/>
     </row>
-    <row r="136">
+    <row r="136" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P136" s="2"/>
       <c r="S136" s="2"/>
     </row>
-    <row r="137">
+    <row r="137" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P137" s="2"/>
       <c r="S137" s="2"/>
     </row>
-    <row r="138">
+    <row r="138" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P138" s="2"/>
       <c r="S138" s="2"/>
     </row>
-    <row r="139">
+    <row r="139" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P139" s="2"/>
       <c r="S139" s="2"/>
     </row>
-    <row r="140">
+    <row r="140" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P140" s="2"/>
       <c r="S140" s="2"/>
     </row>
-    <row r="141">
+    <row r="141" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P141" s="2"/>
       <c r="S141" s="2"/>
     </row>
-    <row r="142">
+    <row r="142" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P142" s="2"/>
       <c r="S142" s="2"/>
     </row>
-    <row r="143">
+    <row r="143" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P143" s="2"/>
       <c r="S143" s="2"/>
     </row>
-    <row r="144">
+    <row r="144" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P144" s="2"/>
       <c r="S144" s="2"/>
     </row>
-    <row r="145">
+    <row r="145" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P145" s="2"/>
       <c r="S145" s="2"/>
     </row>
-    <row r="146">
+    <row r="146" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P146" s="2"/>
       <c r="S146" s="2"/>
     </row>
-    <row r="147">
+    <row r="147" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P147" s="2"/>
       <c r="S147" s="2"/>
     </row>
-    <row r="148">
+    <row r="148" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P148" s="2"/>
       <c r="S148" s="2"/>
     </row>
-    <row r="149">
+    <row r="149" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P149" s="2"/>
       <c r="S149" s="2"/>
     </row>
-    <row r="150">
+    <row r="150" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P150" s="2"/>
       <c r="S150" s="2"/>
     </row>
-    <row r="151">
+    <row r="151" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P151" s="2"/>
       <c r="S151" s="2"/>
     </row>
-    <row r="152">
+    <row r="152" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P152" s="2"/>
       <c r="S152" s="2"/>
     </row>
-    <row r="153">
+    <row r="153" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P153" s="2"/>
       <c r="S153" s="2"/>
     </row>
-    <row r="154">
+    <row r="154" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P154" s="2"/>
       <c r="S154" s="2"/>
     </row>
-    <row r="155">
+    <row r="155" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P155" s="2"/>
       <c r="S155" s="2"/>
     </row>
-    <row r="156">
+    <row r="156" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P156" s="2"/>
       <c r="S156" s="2"/>
     </row>
-    <row r="157">
+    <row r="157" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P157" s="2"/>
       <c r="S157" s="2"/>
     </row>
-    <row r="158">
+    <row r="158" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P158" s="2"/>
       <c r="S158" s="2"/>
     </row>
-    <row r="159">
+    <row r="159" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P159" s="2"/>
       <c r="S159" s="2"/>
     </row>
-    <row r="160">
+    <row r="160" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P160" s="2"/>
       <c r="S160" s="2"/>
     </row>
-    <row r="161">
+    <row r="161" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P161" s="2"/>
       <c r="S161" s="2"/>
     </row>
-    <row r="162">
+    <row r="162" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P162" s="2"/>
       <c r="S162" s="2"/>
     </row>
-    <row r="163">
+    <row r="163" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P163" s="2"/>
       <c r="S163" s="2"/>
     </row>
-    <row r="164">
+    <row r="164" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P164" s="2"/>
       <c r="S164" s="2"/>
     </row>
-    <row r="165">
+    <row r="165" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P165" s="2"/>
       <c r="S165" s="2"/>
     </row>
-    <row r="166">
+    <row r="166" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P166" s="2"/>
       <c r="S166" s="2"/>
     </row>
-    <row r="167">
+    <row r="167" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P167" s="2"/>
       <c r="S167" s="2"/>
     </row>
-    <row r="168">
+    <row r="168" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P168" s="2"/>
       <c r="S168" s="2"/>
     </row>
-    <row r="169">
+    <row r="169" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P169" s="2"/>
       <c r="S169" s="2"/>
     </row>
-    <row r="170">
+    <row r="170" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P170" s="2"/>
       <c r="S170" s="2"/>
     </row>
-    <row r="171">
+    <row r="171" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P171" s="2"/>
       <c r="S171" s="2"/>
     </row>
-    <row r="172">
+    <row r="172" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P172" s="2"/>
       <c r="S172" s="2"/>
     </row>
-    <row r="173">
+    <row r="173" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P173" s="2"/>
       <c r="S173" s="2"/>
     </row>
-    <row r="174">
+    <row r="174" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P174" s="2"/>
       <c r="S174" s="2"/>
     </row>
-    <row r="175">
+    <row r="175" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P175" s="2"/>
       <c r="S175" s="2"/>
     </row>
-    <row r="176">
+    <row r="176" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P176" s="2"/>
       <c r="S176" s="2"/>
     </row>
-    <row r="177">
+    <row r="177" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P177" s="2"/>
       <c r="S177" s="2"/>
     </row>
-    <row r="178">
+    <row r="178" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P178" s="2"/>
       <c r="S178" s="2"/>
     </row>
-    <row r="179">
+    <row r="179" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P179" s="2"/>
       <c r="S179" s="2"/>
     </row>
-    <row r="180">
+    <row r="180" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P180" s="2"/>
       <c r="S180" s="2"/>
     </row>
-    <row r="181">
+    <row r="181" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P181" s="2"/>
       <c r="S181" s="2"/>
     </row>
-    <row r="182">
+    <row r="182" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P182" s="2"/>
       <c r="S182" s="2"/>
     </row>
-    <row r="183">
+    <row r="183" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P183" s="2"/>
       <c r="S183" s="2"/>
     </row>
-    <row r="184">
+    <row r="184" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P184" s="2"/>
       <c r="S184" s="2"/>
     </row>
-    <row r="185">
+    <row r="185" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P185" s="2"/>
       <c r="S185" s="2"/>
     </row>
-    <row r="186">
+    <row r="186" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P186" s="2"/>
       <c r="S186" s="2"/>
     </row>
-    <row r="187">
+    <row r="187" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P187" s="2"/>
       <c r="S187" s="2"/>
     </row>
-    <row r="188">
+    <row r="188" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P188" s="2"/>
       <c r="S188" s="2"/>
     </row>
-    <row r="189">
+    <row r="189" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P189" s="2"/>
       <c r="S189" s="2"/>
     </row>
-    <row r="190">
+    <row r="190" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P190" s="2"/>
       <c r="S190" s="2"/>
     </row>
-    <row r="191">
+    <row r="191" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P191" s="2"/>
       <c r="S191" s="2"/>
     </row>
-    <row r="192">
+    <row r="192" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P192" s="2"/>
       <c r="S192" s="2"/>
     </row>
-    <row r="193">
+    <row r="193" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P193" s="2"/>
       <c r="S193" s="2"/>
     </row>
-    <row r="194">
+    <row r="194" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P194" s="2"/>
       <c r="S194" s="2"/>
     </row>
-    <row r="195">
+    <row r="195" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P195" s="2"/>
       <c r="S195" s="2"/>
     </row>
-    <row r="196">
+    <row r="196" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P196" s="2"/>
       <c r="S196" s="2"/>
     </row>
-    <row r="197">
+    <row r="197" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P197" s="2"/>
       <c r="S197" s="2"/>
     </row>
-    <row r="198">
+    <row r="198" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P198" s="2"/>
       <c r="S198" s="2"/>
     </row>
-    <row r="199">
+    <row r="199" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P199" s="2"/>
       <c r="S199" s="2"/>
     </row>
-    <row r="200">
+    <row r="200" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P200" s="2"/>
       <c r="S200" s="2"/>
     </row>
-    <row r="201">
+    <row r="201" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P201" s="2"/>
       <c r="S201" s="2"/>
     </row>
-    <row r="202">
+    <row r="202" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P202" s="2"/>
       <c r="S202" s="2"/>
     </row>
-    <row r="203">
+    <row r="203" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P203" s="2"/>
       <c r="S203" s="2"/>
     </row>
-    <row r="204">
+    <row r="204" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P204" s="2"/>
       <c r="S204" s="2"/>
     </row>
-    <row r="205">
+    <row r="205" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P205" s="2"/>
       <c r="S205" s="2"/>
     </row>
-    <row r="206">
+    <row r="206" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P206" s="2"/>
       <c r="S206" s="2"/>
     </row>
-    <row r="207">
+    <row r="207" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P207" s="2"/>
       <c r="S207" s="2"/>
     </row>
-    <row r="208">
+    <row r="208" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P208" s="2"/>
       <c r="S208" s="2"/>
     </row>
-    <row r="209">
+    <row r="209" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P209" s="2"/>
       <c r="S209" s="2"/>
     </row>
-    <row r="210">
+    <row r="210" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P210" s="2"/>
       <c r="S210" s="2"/>
     </row>
-    <row r="211">
+    <row r="211" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P211" s="2"/>
       <c r="S211" s="2"/>
     </row>
-    <row r="212">
+    <row r="212" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P212" s="2"/>
       <c r="S212" s="2"/>
     </row>
-    <row r="213">
+    <row r="213" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P213" s="2"/>
       <c r="S213" s="2"/>
     </row>
-    <row r="214">
+    <row r="214" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P214" s="2"/>
       <c r="S214" s="2"/>
     </row>
-    <row r="215">
+    <row r="215" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P215" s="2"/>
       <c r="S215" s="2"/>
     </row>
-    <row r="216">
+    <row r="216" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P216" s="2"/>
       <c r="S216" s="2"/>
     </row>
-    <row r="217">
+    <row r="217" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P217" s="2"/>
       <c r="S217" s="2"/>
     </row>
-    <row r="218">
+    <row r="218" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P218" s="2"/>
       <c r="S218" s="2"/>
     </row>
-    <row r="219">
+    <row r="219" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P219" s="2"/>
       <c r="S219" s="2"/>
     </row>
-    <row r="220">
+    <row r="220" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P220" s="2"/>
       <c r="S220" s="2"/>
     </row>
-    <row r="221">
+    <row r="221" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P221" s="2"/>
       <c r="S221" s="2"/>
     </row>
-    <row r="222">
+    <row r="222" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P222" s="2"/>
       <c r="S222" s="2"/>
     </row>
-    <row r="223">
+    <row r="223" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P223" s="2"/>
       <c r="S223" s="2"/>
     </row>
-    <row r="224">
+    <row r="224" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P224" s="2"/>
       <c r="S224" s="2"/>
     </row>
-    <row r="225">
+    <row r="225" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P225" s="2"/>
       <c r="S225" s="2"/>
     </row>
-    <row r="226">
+    <row r="226" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P226" s="2"/>
       <c r="S226" s="2"/>
     </row>
-    <row r="227">
+    <row r="227" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P227" s="2"/>
       <c r="S227" s="2"/>
     </row>
-    <row r="228">
+    <row r="228" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P228" s="2"/>
       <c r="S228" s="2"/>
     </row>
-    <row r="229">
+    <row r="229" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P229" s="2"/>
       <c r="S229" s="2"/>
     </row>
-    <row r="230">
+    <row r="230" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P230" s="2"/>
       <c r="S230" s="2"/>
     </row>
-    <row r="231">
+    <row r="231" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P231" s="2"/>
       <c r="S231" s="2"/>
     </row>
-    <row r="232">
+    <row r="232" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P232" s="2"/>
       <c r="S232" s="2"/>
     </row>
-    <row r="233">
+    <row r="233" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P233" s="2"/>
       <c r="S233" s="2"/>
     </row>
-    <row r="234">
+    <row r="234" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P234" s="2"/>
       <c r="S234" s="2"/>
     </row>
-    <row r="235">
+    <row r="235" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P235" s="2"/>
       <c r="S235" s="2"/>
     </row>
-    <row r="236">
+    <row r="236" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P236" s="2"/>
       <c r="S236" s="2"/>
     </row>
-    <row r="237">
+    <row r="237" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P237" s="2"/>
       <c r="S237" s="2"/>
     </row>
-    <row r="238">
+    <row r="238" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P238" s="2"/>
       <c r="S238" s="2"/>
     </row>
-    <row r="239">
+    <row r="239" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P239" s="2"/>
       <c r="S239" s="2"/>
     </row>
-    <row r="240">
+    <row r="240" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P240" s="2"/>
       <c r="S240" s="2"/>
     </row>
-    <row r="241">
+    <row r="241" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P241" s="2"/>
       <c r="S241" s="2"/>
     </row>
-    <row r="242">
+    <row r="242" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P242" s="2"/>
       <c r="S242" s="2"/>
     </row>
-    <row r="243">
+    <row r="243" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P243" s="2"/>
       <c r="S243" s="2"/>
     </row>
-    <row r="244">
+    <row r="244" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P244" s="2"/>
       <c r="S244" s="2"/>
     </row>
-    <row r="245">
+    <row r="245" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P245" s="2"/>
       <c r="S245" s="2"/>
     </row>
-    <row r="246">
+    <row r="246" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P246" s="2"/>
       <c r="S246" s="2"/>
     </row>
-    <row r="247">
+    <row r="247" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P247" s="2"/>
       <c r="S247" s="2"/>
     </row>
-    <row r="248">
+    <row r="248" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P248" s="2"/>
       <c r="S248" s="2"/>
     </row>
-    <row r="249">
+    <row r="249" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P249" s="2"/>
       <c r="S249" s="2"/>
     </row>
-    <row r="250">
+    <row r="250" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P250" s="2"/>
       <c r="S250" s="2"/>
     </row>
-    <row r="251">
+    <row r="251" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P251" s="2"/>
       <c r="S251" s="2"/>
     </row>
-    <row r="252">
+    <row r="252" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P252" s="2"/>
       <c r="S252" s="2"/>
     </row>
-    <row r="253">
+    <row r="253" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P253" s="2"/>
       <c r="S253" s="2"/>
     </row>
-    <row r="254">
+    <row r="254" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P254" s="2"/>
       <c r="S254" s="2"/>
     </row>
-    <row r="255">
+    <row r="255" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P255" s="2"/>
       <c r="S255" s="2"/>
     </row>
-    <row r="256">
+    <row r="256" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P256" s="2"/>
       <c r="S256" s="2"/>
     </row>
-    <row r="257">
+    <row r="257" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P257" s="2"/>
       <c r="S257" s="2"/>
     </row>
-    <row r="258">
+    <row r="258" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P258" s="2"/>
       <c r="S258" s="2"/>
     </row>
-    <row r="259">
+    <row r="259" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P259" s="2"/>
       <c r="S259" s="2"/>
     </row>
-    <row r="260">
+    <row r="260" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P260" s="2"/>
       <c r="S260" s="2"/>
     </row>
-    <row r="261">
+    <row r="261" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P261" s="2"/>
       <c r="S261" s="2"/>
     </row>
-    <row r="262">
+    <row r="262" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P262" s="2"/>
       <c r="S262" s="2"/>
     </row>
-    <row r="263">
+    <row r="263" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P263" s="2"/>
       <c r="S263" s="2"/>
     </row>
-    <row r="264">
+    <row r="264" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P264" s="2"/>
       <c r="S264" s="2"/>
     </row>
-    <row r="265">
+    <row r="265" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P265" s="2"/>
       <c r="S265" s="2"/>
     </row>
-    <row r="266">
+    <row r="266" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P266" s="2"/>
       <c r="S266" s="2"/>
     </row>
-    <row r="267">
+    <row r="267" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P267" s="2"/>
       <c r="S267" s="2"/>
     </row>
-    <row r="268">
+    <row r="268" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P268" s="2"/>
       <c r="S268" s="2"/>
     </row>
-    <row r="269">
+    <row r="269" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P269" s="2"/>
       <c r="S269" s="2"/>
     </row>
-    <row r="270">
+    <row r="270" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P270" s="2"/>
       <c r="S270" s="2"/>
     </row>
-    <row r="271">
+    <row r="271" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P271" s="2"/>
       <c r="S271" s="2"/>
     </row>
-    <row r="272">
+    <row r="272" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P272" s="2"/>
       <c r="S272" s="2"/>
     </row>
-    <row r="273">
+    <row r="273" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P273" s="2"/>
       <c r="S273" s="2"/>
     </row>
-    <row r="274">
+    <row r="274" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P274" s="2"/>
       <c r="S274" s="2"/>
     </row>
-    <row r="275">
+    <row r="275" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P275" s="2"/>
       <c r="S275" s="2"/>
     </row>
-    <row r="276">
+    <row r="276" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P276" s="2"/>
       <c r="S276" s="2"/>
     </row>
-    <row r="277">
+    <row r="277" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P277" s="2"/>
       <c r="S277" s="2"/>
     </row>
-    <row r="278">
+    <row r="278" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P278" s="2"/>
       <c r="S278" s="2"/>
     </row>
-    <row r="279">
+    <row r="279" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P279" s="2"/>
       <c r="S279" s="2"/>
     </row>
-    <row r="280">
+    <row r="280" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P280" s="2"/>
       <c r="S280" s="2"/>
     </row>
-    <row r="281">
+    <row r="281" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P281" s="2"/>
       <c r="S281" s="2"/>
     </row>
-    <row r="282">
+    <row r="282" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P282" s="2"/>
       <c r="S282" s="2"/>
     </row>
-    <row r="283">
+    <row r="283" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P283" s="2"/>
       <c r="S283" s="2"/>
     </row>
-    <row r="284">
+    <row r="284" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P284" s="2"/>
       <c r="S284" s="2"/>
     </row>
-    <row r="285">
+    <row r="285" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P285" s="2"/>
       <c r="S285" s="2"/>
     </row>
-    <row r="286">
+    <row r="286" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P286" s="2"/>
       <c r="S286" s="2"/>
     </row>
-    <row r="287">
+    <row r="287" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P287" s="2"/>
       <c r="S287" s="2"/>
     </row>
-    <row r="288">
+    <row r="288" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P288" s="2"/>
       <c r="S288" s="2"/>
     </row>
-    <row r="289">
+    <row r="289" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P289" s="2"/>
       <c r="S289" s="2"/>
     </row>
-    <row r="290">
+    <row r="290" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P290" s="2"/>
       <c r="S290" s="2"/>
     </row>
-    <row r="291">
+    <row r="291" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P291" s="2"/>
       <c r="S291" s="2"/>
     </row>
-    <row r="292">
+    <row r="292" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P292" s="2"/>
       <c r="S292" s="2"/>
     </row>
-    <row r="293">
+    <row r="293" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P293" s="2"/>
       <c r="S293" s="2"/>
     </row>
-    <row r="294">
+    <row r="294" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P294" s="2"/>
       <c r="S294" s="2"/>
     </row>
-    <row r="295">
+    <row r="295" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P295" s="2"/>
       <c r="S295" s="2"/>
     </row>
-    <row r="296">
+    <row r="296" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P296" s="2"/>
       <c r="S296" s="2"/>
     </row>
-    <row r="297">
+    <row r="297" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P297" s="2"/>
       <c r="S297" s="2"/>
     </row>
-    <row r="298">
+    <row r="298" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P298" s="2"/>
       <c r="S298" s="2"/>
     </row>
-    <row r="299">
+    <row r="299" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P299" s="2"/>
       <c r="S299" s="2"/>
     </row>
-    <row r="300">
+    <row r="300" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P300" s="2"/>
       <c r="S300" s="2"/>
     </row>
-    <row r="301">
+    <row r="301" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P301" s="2"/>
       <c r="S301" s="2"/>
     </row>
-    <row r="302">
+    <row r="302" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P302" s="2"/>
       <c r="S302" s="2"/>
     </row>
-    <row r="303">
+    <row r="303" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P303" s="2"/>
       <c r="S303" s="2"/>
     </row>
-    <row r="304">
+    <row r="304" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P304" s="2"/>
       <c r="S304" s="2"/>
     </row>
-    <row r="305">
+    <row r="305" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P305" s="2"/>
       <c r="S305" s="2"/>
     </row>
-    <row r="306">
+    <row r="306" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P306" s="2"/>
       <c r="S306" s="2"/>
     </row>
-    <row r="307">
+    <row r="307" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P307" s="2"/>
       <c r="S307" s="2"/>
     </row>
-    <row r="308">
+    <row r="308" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P308" s="2"/>
       <c r="S308" s="2"/>
     </row>
-    <row r="309">
+    <row r="309" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P309" s="2"/>
       <c r="S309" s="2"/>
     </row>
-    <row r="310">
+    <row r="310" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P310" s="2"/>
       <c r="S310" s="2"/>
     </row>
-    <row r="311">
+    <row r="311" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P311" s="2"/>
       <c r="S311" s="2"/>
     </row>
-    <row r="312">
+    <row r="312" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P312" s="2"/>
       <c r="S312" s="2"/>
     </row>
-    <row r="313">
+    <row r="313" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P313" s="2"/>
       <c r="S313" s="2"/>
     </row>
-    <row r="314">
+    <row r="314" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P314" s="2"/>
       <c r="S314" s="2"/>
     </row>
-    <row r="315">
+    <row r="315" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P315" s="2"/>
       <c r="S315" s="2"/>
     </row>
-    <row r="316">
+    <row r="316" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P316" s="2"/>
       <c r="S316" s="2"/>
     </row>
-    <row r="317">
+    <row r="317" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P317" s="2"/>
       <c r="S317" s="2"/>
     </row>
-    <row r="318">
+    <row r="318" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P318" s="2"/>
       <c r="S318" s="2"/>
     </row>
-    <row r="319">
+    <row r="319" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P319" s="2"/>
       <c r="S319" s="2"/>
     </row>
-    <row r="320">
+    <row r="320" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P320" s="2"/>
       <c r="S320" s="2"/>
     </row>
-    <row r="321">
+    <row r="321" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P321" s="2"/>
       <c r="S321" s="2"/>
     </row>
-    <row r="322">
+    <row r="322" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P322" s="2"/>
       <c r="S322" s="2"/>
     </row>
-    <row r="323">
+    <row r="323" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P323" s="2"/>
       <c r="S323" s="2"/>
     </row>
-    <row r="324">
+    <row r="324" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P324" s="2"/>
       <c r="S324" s="2"/>
     </row>
-    <row r="325">
+    <row r="325" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P325" s="2"/>
       <c r="S325" s="2"/>
     </row>
-    <row r="326">
+    <row r="326" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P326" s="2"/>
       <c r="S326" s="2"/>
     </row>
-    <row r="327">
+    <row r="327" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P327" s="2"/>
       <c r="S327" s="2"/>
     </row>
-    <row r="328">
+    <row r="328" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P328" s="2"/>
       <c r="S328" s="2"/>
     </row>
-    <row r="329">
+    <row r="329" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P329" s="2"/>
       <c r="S329" s="2"/>
     </row>
-    <row r="330">
+    <row r="330" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P330" s="2"/>
       <c r="S330" s="2"/>
     </row>
-    <row r="331">
+    <row r="331" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P331" s="2"/>
       <c r="S331" s="2"/>
     </row>
-    <row r="332">
+    <row r="332" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P332" s="2"/>
       <c r="S332" s="2"/>
     </row>
-    <row r="333">
+    <row r="333" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P333" s="2"/>
       <c r="S333" s="2"/>
     </row>
-    <row r="334">
+    <row r="334" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P334" s="2"/>
       <c r="S334" s="2"/>
     </row>
-    <row r="335">
+    <row r="335" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P335" s="2"/>
       <c r="S335" s="2"/>
     </row>
-    <row r="336">
+    <row r="336" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P336" s="2"/>
       <c r="S336" s="2"/>
     </row>
-    <row r="337">
+    <row r="337" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P337" s="2"/>
       <c r="S337" s="2"/>
     </row>
-    <row r="338">
+    <row r="338" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P338" s="2"/>
       <c r="S338" s="2"/>
     </row>
-    <row r="339">
+    <row r="339" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P339" s="2"/>
       <c r="S339" s="2"/>
     </row>
-    <row r="340">
+    <row r="340" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P340" s="2"/>
       <c r="S340" s="2"/>
     </row>
-    <row r="341">
+    <row r="341" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P341" s="2"/>
       <c r="S341" s="2"/>
     </row>
-    <row r="342">
+    <row r="342" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P342" s="2"/>
       <c r="S342" s="2"/>
     </row>
-    <row r="343">
+    <row r="343" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P343" s="2"/>
       <c r="S343" s="2"/>
     </row>
-    <row r="344">
+    <row r="344" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P344" s="2"/>
       <c r="S344" s="2"/>
     </row>
-    <row r="345">
+    <row r="345" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P345" s="2"/>
       <c r="S345" s="2"/>
     </row>
-    <row r="346">
+    <row r="346" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P346" s="2"/>
       <c r="S346" s="2"/>
     </row>
-    <row r="347">
+    <row r="347" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P347" s="2"/>
       <c r="S347" s="2"/>
     </row>
-    <row r="348">
+    <row r="348" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P348" s="2"/>
       <c r="S348" s="2"/>
     </row>
-    <row r="349">
+    <row r="349" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P349" s="2"/>
       <c r="S349" s="2"/>
     </row>
-    <row r="350">
+    <row r="350" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P350" s="2"/>
       <c r="S350" s="2"/>
     </row>
-    <row r="351">
+    <row r="351" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P351" s="2"/>
       <c r="S351" s="2"/>
     </row>
-    <row r="352">
+    <row r="352" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P352" s="2"/>
       <c r="S352" s="2"/>
     </row>
-    <row r="353">
+    <row r="353" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P353" s="2"/>
       <c r="S353" s="2"/>
     </row>
-    <row r="354">
+    <row r="354" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P354" s="2"/>
       <c r="S354" s="2"/>
     </row>
-    <row r="355">
+    <row r="355" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P355" s="2"/>
       <c r="S355" s="2"/>
     </row>
-    <row r="356">
+    <row r="356" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P356" s="2"/>
       <c r="S356" s="2"/>
     </row>
-    <row r="357">
+    <row r="357" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P357" s="2"/>
       <c r="S357" s="2"/>
     </row>
-    <row r="358">
+    <row r="358" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P358" s="2"/>
       <c r="S358" s="2"/>
     </row>
-    <row r="359">
+    <row r="359" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P359" s="2"/>
       <c r="S359" s="2"/>
     </row>
-    <row r="360">
+    <row r="360" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P360" s="2"/>
       <c r="S360" s="2"/>
     </row>
-    <row r="361">
+    <row r="361" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P361" s="2"/>
       <c r="S361" s="2"/>
     </row>
-    <row r="362">
+    <row r="362" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P362" s="2"/>
       <c r="S362" s="2"/>
     </row>
-    <row r="363">
+    <row r="363" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P363" s="2"/>
       <c r="S363" s="2"/>
     </row>
-    <row r="364">
+    <row r="364" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P364" s="2"/>
       <c r="S364" s="2"/>
     </row>
-    <row r="365">
+    <row r="365" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P365" s="2"/>
       <c r="S365" s="2"/>
     </row>
-    <row r="366">
+    <row r="366" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P366" s="2"/>
       <c r="S366" s="2"/>
     </row>
-    <row r="367">
+    <row r="367" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P367" s="2"/>
       <c r="S367" s="2"/>
     </row>
-    <row r="368">
+    <row r="368" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P368" s="2"/>
       <c r="S368" s="2"/>
     </row>
-    <row r="369">
+    <row r="369" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P369" s="2"/>
       <c r="S369" s="2"/>
     </row>
-    <row r="370">
+    <row r="370" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P370" s="2"/>
       <c r="S370" s="2"/>
     </row>
-    <row r="371">
+    <row r="371" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P371" s="2"/>
       <c r="S371" s="2"/>
     </row>
-    <row r="372">
+    <row r="372" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P372" s="2"/>
       <c r="S372" s="2"/>
     </row>
-    <row r="373">
+    <row r="373" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P373" s="2"/>
       <c r="S373" s="2"/>
     </row>
-    <row r="374">
+    <row r="374" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P374" s="2"/>
       <c r="S374" s="2"/>
     </row>
-    <row r="375">
+    <row r="375" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P375" s="2"/>
       <c r="S375" s="2"/>
     </row>
-    <row r="376">
+    <row r="376" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P376" s="2"/>
       <c r="S376" s="2"/>
     </row>
-    <row r="377">
+    <row r="377" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P377" s="2"/>
       <c r="S377" s="2"/>
     </row>
-    <row r="378">
+    <row r="378" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P378" s="2"/>
       <c r="S378" s="2"/>
     </row>
-    <row r="379">
+    <row r="379" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P379" s="2"/>
       <c r="S379" s="2"/>
     </row>
-    <row r="380">
+    <row r="380" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P380" s="2"/>
       <c r="S380" s="2"/>
     </row>
-    <row r="381">
+    <row r="381" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P381" s="2"/>
       <c r="S381" s="2"/>
     </row>
-    <row r="382">
+    <row r="382" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P382" s="2"/>
       <c r="S382" s="2"/>
     </row>
-    <row r="383">
+    <row r="383" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P383" s="2"/>
       <c r="S383" s="2"/>
     </row>
-    <row r="384">
+    <row r="384" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P384" s="2"/>
       <c r="S384" s="2"/>
     </row>
-    <row r="385">
+    <row r="385" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P385" s="2"/>
       <c r="S385" s="2"/>
     </row>
-    <row r="386">
+    <row r="386" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P386" s="2"/>
       <c r="S386" s="2"/>
     </row>
-    <row r="387">
+    <row r="387" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P387" s="2"/>
       <c r="S387" s="2"/>
     </row>
-    <row r="388">
+    <row r="388" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P388" s="2"/>
       <c r="S388" s="2"/>
     </row>
-    <row r="389">
+    <row r="389" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P389" s="2"/>
       <c r="S389" s="2"/>
     </row>
-    <row r="390">
+    <row r="390" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P390" s="2"/>
       <c r="S390" s="2"/>
     </row>
-    <row r="391">
+    <row r="391" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P391" s="2"/>
       <c r="S391" s="2"/>
     </row>
-    <row r="392">
+    <row r="392" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P392" s="2"/>
       <c r="S392" s="2"/>
     </row>
-    <row r="393">
+    <row r="393" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P393" s="2"/>
       <c r="S393" s="2"/>
     </row>
-    <row r="394">
+    <row r="394" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P394" s="2"/>
       <c r="S394" s="2"/>
     </row>
-    <row r="395">
+    <row r="395" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P395" s="2"/>
       <c r="S395" s="2"/>
     </row>
-    <row r="396">
+    <row r="396" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P396" s="2"/>
       <c r="S396" s="2"/>
     </row>
-    <row r="397">
+    <row r="397" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P397" s="2"/>
       <c r="S397" s="2"/>
     </row>
-    <row r="398">
+    <row r="398" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P398" s="2"/>
       <c r="S398" s="2"/>
     </row>
-    <row r="399">
+    <row r="399" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P399" s="2"/>
       <c r="S399" s="2"/>
     </row>
-    <row r="400">
+    <row r="400" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P400" s="2"/>
       <c r="S400" s="2"/>
     </row>
-    <row r="401">
+    <row r="401" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P401" s="2"/>
       <c r="S401" s="2"/>
     </row>
-    <row r="402">
+    <row r="402" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P402" s="2"/>
       <c r="S402" s="2"/>
     </row>
-    <row r="403">
+    <row r="403" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P403" s="2"/>
       <c r="S403" s="2"/>
     </row>
-    <row r="404">
+    <row r="404" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P404" s="2"/>
       <c r="S404" s="2"/>
     </row>
-    <row r="405">
+    <row r="405" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P405" s="2"/>
       <c r="S405" s="2"/>
     </row>
-    <row r="406">
+    <row r="406" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P406" s="2"/>
       <c r="S406" s="2"/>
     </row>
-    <row r="407">
+    <row r="407" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P407" s="2"/>
       <c r="S407" s="2"/>
     </row>
-    <row r="408">
+    <row r="408" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P408" s="2"/>
       <c r="S408" s="2"/>
     </row>
-    <row r="409">
+    <row r="409" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P409" s="2"/>
       <c r="S409" s="2"/>
     </row>
-    <row r="410">
+    <row r="410" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P410" s="2"/>
       <c r="S410" s="2"/>
     </row>
-    <row r="411">
+    <row r="411" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P411" s="2"/>
       <c r="S411" s="2"/>
     </row>
-    <row r="412">
+    <row r="412" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P412" s="2"/>
       <c r="S412" s="2"/>
     </row>
-    <row r="413">
+    <row r="413" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P413" s="2"/>
       <c r="S413" s="2"/>
     </row>
-    <row r="414">
+    <row r="414" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P414" s="2"/>
       <c r="S414" s="2"/>
     </row>
-    <row r="415">
+    <row r="415" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P415" s="2"/>
       <c r="S415" s="2"/>
     </row>
-    <row r="416">
+    <row r="416" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P416" s="2"/>
       <c r="S416" s="2"/>
     </row>
-    <row r="417">
+    <row r="417" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P417" s="2"/>
       <c r="S417" s="2"/>
     </row>
-    <row r="418">
+    <row r="418" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P418" s="2"/>
       <c r="S418" s="2"/>
     </row>
-    <row r="419">
+    <row r="419" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P419" s="2"/>
       <c r="S419" s="2"/>
     </row>
-    <row r="420">
+    <row r="420" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P420" s="2"/>
       <c r="S420" s="2"/>
     </row>
-    <row r="421">
+    <row r="421" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P421" s="2"/>
       <c r="S421" s="2"/>
     </row>
-    <row r="422">
+    <row r="422" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P422" s="2"/>
       <c r="S422" s="2"/>
     </row>
-    <row r="423">
+    <row r="423" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P423" s="2"/>
       <c r="S423" s="2"/>
     </row>
-    <row r="424">
+    <row r="424" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P424" s="2"/>
       <c r="S424" s="2"/>
     </row>
-    <row r="425">
+    <row r="425" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P425" s="2"/>
       <c r="S425" s="2"/>
     </row>
-    <row r="426">
+    <row r="426" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P426" s="2"/>
       <c r="S426" s="2"/>
     </row>
-    <row r="427">
+    <row r="427" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P427" s="2"/>
       <c r="S427" s="2"/>
     </row>
-    <row r="428">
+    <row r="428" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P428" s="2"/>
       <c r="S428" s="2"/>
     </row>
-    <row r="429">
+    <row r="429" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P429" s="2"/>
       <c r="S429" s="2"/>
     </row>
-    <row r="430">
+    <row r="430" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P430" s="2"/>
       <c r="S430" s="2"/>
     </row>
-    <row r="431">
+    <row r="431" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P431" s="2"/>
       <c r="S431" s="2"/>
     </row>
-    <row r="432">
+    <row r="432" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P432" s="2"/>
       <c r="S432" s="2"/>
     </row>
-    <row r="433">
+    <row r="433" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P433" s="2"/>
       <c r="S433" s="2"/>
     </row>
-    <row r="434">
+    <row r="434" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P434" s="2"/>
       <c r="S434" s="2"/>
     </row>
-    <row r="435">
+    <row r="435" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P435" s="2"/>
       <c r="S435" s="2"/>
     </row>
-    <row r="436">
+    <row r="436" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P436" s="2"/>
       <c r="S436" s="2"/>
     </row>
-    <row r="437">
+    <row r="437" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P437" s="2"/>
       <c r="S437" s="2"/>
     </row>
-    <row r="438">
+    <row r="438" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P438" s="2"/>
       <c r="S438" s="2"/>
     </row>
-    <row r="439">
+    <row r="439" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P439" s="2"/>
       <c r="S439" s="2"/>
     </row>
-    <row r="440">
+    <row r="440" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P440" s="2"/>
       <c r="S440" s="2"/>
     </row>
-    <row r="441">
+    <row r="441" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P441" s="2"/>
       <c r="S441" s="2"/>
     </row>
-    <row r="442">
+    <row r="442" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P442" s="2"/>
       <c r="S442" s="2"/>
     </row>
-    <row r="443">
+    <row r="443" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P443" s="2"/>
       <c r="S443" s="2"/>
     </row>
-    <row r="444">
+    <row r="444" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P444" s="2"/>
       <c r="S444" s="2"/>
     </row>
-    <row r="445">
+    <row r="445" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P445" s="2"/>
       <c r="S445" s="2"/>
     </row>
-    <row r="446">
+    <row r="446" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P446" s="2"/>
       <c r="S446" s="2"/>
     </row>
-    <row r="447">
+    <row r="447" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P447" s="2"/>
       <c r="S447" s="2"/>
     </row>
-    <row r="448">
+    <row r="448" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P448" s="2"/>
       <c r="S448" s="2"/>
     </row>
-    <row r="449">
+    <row r="449" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P449" s="2"/>
       <c r="S449" s="2"/>
     </row>
-    <row r="450">
+    <row r="450" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P450" s="2"/>
       <c r="S450" s="2"/>
     </row>
-    <row r="451">
+    <row r="451" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P451" s="2"/>
       <c r="S451" s="2"/>
     </row>
-    <row r="452">
+    <row r="452" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P452" s="2"/>
       <c r="S452" s="2"/>
     </row>
-    <row r="453">
+    <row r="453" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P453" s="2"/>
       <c r="S453" s="2"/>
     </row>
-    <row r="454">
+    <row r="454" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P454" s="2"/>
       <c r="S454" s="2"/>
     </row>
-    <row r="455">
+    <row r="455" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P455" s="2"/>
       <c r="S455" s="2"/>
     </row>
-    <row r="456">
+    <row r="456" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P456" s="2"/>
       <c r="S456" s="2"/>
     </row>
-    <row r="457">
+    <row r="457" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P457" s="2"/>
       <c r="S457" s="2"/>
     </row>
-    <row r="458">
+    <row r="458" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P458" s="2"/>
       <c r="S458" s="2"/>
     </row>
-    <row r="459">
+    <row r="459" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P459" s="2"/>
       <c r="S459" s="2"/>
     </row>
-    <row r="460">
+    <row r="460" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P460" s="2"/>
       <c r="S460" s="2"/>
     </row>
-    <row r="461">
+    <row r="461" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P461" s="2"/>
       <c r="S461" s="2"/>
     </row>
-    <row r="462">
+    <row r="462" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P462" s="2"/>
       <c r="S462" s="2"/>
     </row>
-    <row r="463">
+    <row r="463" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P463" s="2"/>
       <c r="S463" s="2"/>
     </row>
-    <row r="464">
+    <row r="464" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P464" s="2"/>
       <c r="S464" s="2"/>
     </row>
-    <row r="465">
+    <row r="465" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P465" s="2"/>
       <c r="S465" s="2"/>
     </row>
-    <row r="466">
+    <row r="466" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P466" s="2"/>
       <c r="S466" s="2"/>
     </row>
-    <row r="467">
+    <row r="467" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P467" s="2"/>
       <c r="S467" s="2"/>
     </row>
-    <row r="468">
+    <row r="468" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P468" s="2"/>
       <c r="S468" s="2"/>
     </row>
-    <row r="469">
+    <row r="469" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P469" s="2"/>
       <c r="S469" s="2"/>
     </row>
-    <row r="470">
+    <row r="470" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P470" s="2"/>
       <c r="S470" s="2"/>
     </row>
-    <row r="471">
+    <row r="471" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P471" s="2"/>
       <c r="S471" s="2"/>
     </row>
-    <row r="472">
+    <row r="472" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P472" s="2"/>
       <c r="S472" s="2"/>
     </row>
-    <row r="473">
+    <row r="473" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P473" s="2"/>
       <c r="S473" s="2"/>
     </row>
-    <row r="474">
+    <row r="474" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P474" s="2"/>
       <c r="S474" s="2"/>
     </row>
-    <row r="475">
+    <row r="475" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P475" s="2"/>
       <c r="S475" s="2"/>
     </row>
-    <row r="476">
+    <row r="476" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P476" s="2"/>
       <c r="S476" s="2"/>
     </row>
-    <row r="477">
+    <row r="477" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P477" s="2"/>
       <c r="S477" s="2"/>
     </row>
-    <row r="478">
+    <row r="478" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P478" s="2"/>
       <c r="S478" s="2"/>
     </row>
-    <row r="479">
+    <row r="479" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P479" s="2"/>
       <c r="S479" s="2"/>
     </row>
-    <row r="480">
+    <row r="480" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P480" s="2"/>
       <c r="S480" s="2"/>
     </row>
-    <row r="481">
+    <row r="481" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P481" s="2"/>
       <c r="S481" s="2"/>
     </row>
-    <row r="482">
+    <row r="482" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P482" s="2"/>
       <c r="S482" s="2"/>
     </row>
-    <row r="483">
+    <row r="483" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P483" s="2"/>
       <c r="S483" s="2"/>
     </row>
-    <row r="484">
+    <row r="484" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P484" s="2"/>
       <c r="S484" s="2"/>
     </row>
-    <row r="485">
+    <row r="485" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P485" s="2"/>
       <c r="S485" s="2"/>
     </row>
-    <row r="486">
+    <row r="486" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P486" s="2"/>
       <c r="S486" s="2"/>
     </row>
-    <row r="487">
+    <row r="487" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P487" s="2"/>
       <c r="S487" s="2"/>
     </row>
-    <row r="488">
+    <row r="488" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P488" s="2"/>
       <c r="S488" s="2"/>
     </row>
-    <row r="489">
+    <row r="489" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P489" s="2"/>
       <c r="S489" s="2"/>
     </row>
-    <row r="490">
+    <row r="490" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P490" s="2"/>
       <c r="S490" s="2"/>
     </row>
-    <row r="491">
+    <row r="491" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P491" s="2"/>
       <c r="S491" s="2"/>
     </row>
-    <row r="492">
+    <row r="492" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P492" s="2"/>
       <c r="S492" s="2"/>
     </row>
-    <row r="493">
+    <row r="493" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P493" s="2"/>
       <c r="S493" s="2"/>
     </row>
-    <row r="494">
+    <row r="494" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P494" s="2"/>
       <c r="S494" s="2"/>
     </row>
-    <row r="495">
+    <row r="495" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P495" s="2"/>
       <c r="S495" s="2"/>
     </row>
-    <row r="496">
+    <row r="496" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P496" s="2"/>
       <c r="S496" s="2"/>
     </row>
-    <row r="497">
+    <row r="497" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P497" s="2"/>
       <c r="S497" s="2"/>
     </row>
-    <row r="498">
+    <row r="498" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P498" s="2"/>
       <c r="S498" s="2"/>
     </row>
-    <row r="499">
+    <row r="499" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P499" s="2"/>
       <c r="S499" s="2"/>
     </row>
-    <row r="500">
+    <row r="500" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P500" s="2"/>
       <c r="S500" s="2"/>
     </row>
-    <row r="501">
+    <row r="501" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P501" s="2"/>
       <c r="S501" s="2"/>
     </row>
-    <row r="502">
+    <row r="502" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P502" s="2"/>
       <c r="S502" s="2"/>
     </row>
-    <row r="503">
+    <row r="503" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P503" s="2"/>
       <c r="S503" s="2"/>
     </row>
-    <row r="504">
+    <row r="504" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P504" s="2"/>
       <c r="S504" s="2"/>
     </row>
-    <row r="505">
+    <row r="505" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P505" s="2"/>
       <c r="S505" s="2"/>
     </row>
-    <row r="506">
+    <row r="506" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P506" s="2"/>
       <c r="S506" s="2"/>
     </row>
-    <row r="507">
+    <row r="507" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P507" s="2"/>
       <c r="S507" s="2"/>
     </row>
-    <row r="508">
+    <row r="508" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P508" s="2"/>
       <c r="S508" s="2"/>
     </row>
-    <row r="509">
+    <row r="509" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P509" s="2"/>
       <c r="S509" s="2"/>
     </row>
-    <row r="510">
+    <row r="510" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P510" s="2"/>
       <c r="S510" s="2"/>
     </row>
-    <row r="511">
+    <row r="511" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P511" s="2"/>
       <c r="S511" s="2"/>
     </row>
-    <row r="512">
+    <row r="512" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P512" s="2"/>
       <c r="S512" s="2"/>
     </row>
-    <row r="513">
+    <row r="513" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P513" s="2"/>
       <c r="S513" s="2"/>
     </row>
-    <row r="514">
+    <row r="514" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P514" s="2"/>
       <c r="S514" s="2"/>
     </row>
-    <row r="515">
+    <row r="515" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P515" s="2"/>
       <c r="S515" s="2"/>
     </row>
-    <row r="516">
+    <row r="516" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P516" s="2"/>
       <c r="S516" s="2"/>
     </row>
-    <row r="517">
+    <row r="517" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P517" s="2"/>
       <c r="S517" s="2"/>
     </row>
-    <row r="518">
+    <row r="518" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P518" s="2"/>
       <c r="S518" s="2"/>
     </row>
-    <row r="519">
+    <row r="519" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P519" s="2"/>
       <c r="S519" s="2"/>
     </row>
-    <row r="520">
+    <row r="520" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P520" s="2"/>
       <c r="S520" s="2"/>
     </row>
-    <row r="521">
+    <row r="521" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P521" s="2"/>
       <c r="S521" s="2"/>
     </row>
-    <row r="522">
+    <row r="522" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P522" s="2"/>
       <c r="S522" s="2"/>
     </row>
-    <row r="523">
+    <row r="523" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P523" s="2"/>
       <c r="S523" s="2"/>
     </row>
-    <row r="524">
+    <row r="524" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P524" s="2"/>
       <c r="S524" s="2"/>
     </row>
-    <row r="525">
+    <row r="525" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P525" s="2"/>
       <c r="S525" s="2"/>
     </row>
-    <row r="526">
+    <row r="526" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P526" s="2"/>
       <c r="S526" s="2"/>
     </row>
-    <row r="527">
+    <row r="527" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P527" s="2"/>
       <c r="S527" s="2"/>
     </row>
-    <row r="528">
+    <row r="528" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P528" s="2"/>
       <c r="S528" s="2"/>
     </row>
-    <row r="529">
+    <row r="529" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P529" s="2"/>
       <c r="S529" s="2"/>
     </row>
-    <row r="530">
+    <row r="530" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P530" s="2"/>
       <c r="S530" s="2"/>
     </row>
-    <row r="531">
+    <row r="531" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P531" s="2"/>
       <c r="S531" s="2"/>
     </row>
-    <row r="532">
+    <row r="532" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P532" s="2"/>
       <c r="S532" s="2"/>
     </row>
-    <row r="533">
+    <row r="533" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P533" s="2"/>
       <c r="S533" s="2"/>
     </row>
-    <row r="534">
+    <row r="534" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P534" s="2"/>
       <c r="S534" s="2"/>
     </row>
-    <row r="535">
+    <row r="535" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P535" s="2"/>
       <c r="S535" s="2"/>
     </row>
-    <row r="536">
+    <row r="536" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P536" s="2"/>
       <c r="S536" s="2"/>
     </row>
-    <row r="537">
+    <row r="537" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P537" s="2"/>
       <c r="S537" s="2"/>
     </row>
-    <row r="538">
+    <row r="538" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P538" s="2"/>
       <c r="S538" s="2"/>
     </row>
-    <row r="539">
+    <row r="539" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P539" s="2"/>
       <c r="S539" s="2"/>
     </row>
-    <row r="540">
+    <row r="540" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P540" s="2"/>
       <c r="S540" s="2"/>
     </row>
-    <row r="541">
+    <row r="541" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P541" s="2"/>
       <c r="S541" s="2"/>
     </row>
-    <row r="542">
+    <row r="542" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P542" s="2"/>
       <c r="S542" s="2"/>
     </row>
-    <row r="543">
+    <row r="543" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P543" s="2"/>
       <c r="S543" s="2"/>
     </row>
-    <row r="544">
+    <row r="544" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P544" s="2"/>
       <c r="S544" s="2"/>
     </row>
-    <row r="545">
+    <row r="545" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P545" s="2"/>
       <c r="S545" s="2"/>
     </row>
-    <row r="546">
+    <row r="546" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P546" s="2"/>
       <c r="S546" s="2"/>
     </row>
-    <row r="547">
+    <row r="547" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P547" s="2"/>
       <c r="S547" s="2"/>
     </row>
-    <row r="548">
+    <row r="548" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P548" s="2"/>
       <c r="S548" s="2"/>
     </row>
-    <row r="549">
+    <row r="549" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P549" s="2"/>
       <c r="S549" s="2"/>
     </row>
-    <row r="550">
+    <row r="550" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P550" s="2"/>
       <c r="S550" s="2"/>
     </row>
-    <row r="551">
+    <row r="551" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P551" s="2"/>
       <c r="S551" s="2"/>
     </row>
-    <row r="552">
+    <row r="552" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P552" s="2"/>
       <c r="S552" s="2"/>
     </row>
-    <row r="553">
+    <row r="553" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P553" s="2"/>
       <c r="S553" s="2"/>
     </row>
-    <row r="554">
+    <row r="554" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P554" s="2"/>
       <c r="S554" s="2"/>
     </row>
-    <row r="555">
+    <row r="555" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P555" s="2"/>
       <c r="S555" s="2"/>
     </row>
-    <row r="556">
+    <row r="556" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P556" s="2"/>
       <c r="S556" s="2"/>
     </row>
-    <row r="557">
+    <row r="557" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P557" s="2"/>
       <c r="S557" s="2"/>
     </row>
-    <row r="558">
+    <row r="558" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P558" s="2"/>
       <c r="S558" s="2"/>
     </row>
-    <row r="559">
+    <row r="559" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P559" s="2"/>
       <c r="S559" s="2"/>
     </row>
-    <row r="560">
+    <row r="560" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P560" s="2"/>
       <c r="S560" s="2"/>
     </row>
-    <row r="561">
+    <row r="561" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P561" s="2"/>
       <c r="S561" s="2"/>
     </row>
-    <row r="562">
+    <row r="562" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P562" s="2"/>
       <c r="S562" s="2"/>
     </row>
-    <row r="563">
+    <row r="563" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P563" s="2"/>
       <c r="S563" s="2"/>
     </row>
-    <row r="564">
+    <row r="564" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P564" s="2"/>
       <c r="S564" s="2"/>
     </row>
-    <row r="565">
+    <row r="565" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P565" s="2"/>
       <c r="S565" s="2"/>
     </row>
-    <row r="566">
+    <row r="566" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P566" s="2"/>
       <c r="S566" s="2"/>
     </row>
-    <row r="567">
+    <row r="567" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P567" s="2"/>
       <c r="S567" s="2"/>
     </row>
-    <row r="568">
+    <row r="568" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P568" s="2"/>
       <c r="S568" s="2"/>
     </row>
-    <row r="569">
+    <row r="569" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P569" s="2"/>
       <c r="S569" s="2"/>
     </row>
-    <row r="570">
+    <row r="570" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P570" s="2"/>
       <c r="S570" s="2"/>
     </row>
-    <row r="571">
+    <row r="571" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P571" s="2"/>
       <c r="S571" s="2"/>
     </row>
-    <row r="572">
+    <row r="572" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P572" s="2"/>
       <c r="S572" s="2"/>
     </row>
-    <row r="573">
+    <row r="573" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P573" s="2"/>
       <c r="S573" s="2"/>
     </row>
-    <row r="574">
+    <row r="574" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P574" s="2"/>
       <c r="S574" s="2"/>
     </row>
-    <row r="575">
+    <row r="575" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P575" s="2"/>
       <c r="S575" s="2"/>
     </row>
-    <row r="576">
+    <row r="576" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P576" s="2"/>
       <c r="S576" s="2"/>
     </row>
-    <row r="577">
+    <row r="577" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P577" s="2"/>
       <c r="S577" s="2"/>
     </row>
-    <row r="578">
+    <row r="578" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P578" s="2"/>
       <c r="S578" s="2"/>
     </row>
-    <row r="579">
+    <row r="579" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P579" s="2"/>
       <c r="S579" s="2"/>
     </row>
-    <row r="580">
+    <row r="580" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P580" s="2"/>
       <c r="S580" s="2"/>
     </row>
-    <row r="581">
+    <row r="581" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P581" s="2"/>
       <c r="S581" s="2"/>
     </row>
-    <row r="582">
+    <row r="582" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P582" s="2"/>
       <c r="S582" s="2"/>
     </row>
-    <row r="583">
+    <row r="583" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P583" s="2"/>
       <c r="S583" s="2"/>
     </row>
-    <row r="584">
+    <row r="584" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P584" s="2"/>
       <c r="S584" s="2"/>
     </row>
-    <row r="585">
+    <row r="585" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P585" s="2"/>
       <c r="S585" s="2"/>
     </row>
-    <row r="586">
+    <row r="586" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P586" s="2"/>
       <c r="S586" s="2"/>
     </row>
-    <row r="587">
+    <row r="587" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P587" s="2"/>
       <c r="S587" s="2"/>
     </row>
-    <row r="588">
+    <row r="588" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P588" s="2"/>
       <c r="S588" s="2"/>
     </row>
-    <row r="589">
+    <row r="589" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P589" s="2"/>
       <c r="S589" s="2"/>
     </row>
-    <row r="590">
+    <row r="590" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P590" s="2"/>
       <c r="S590" s="2"/>
     </row>
-    <row r="591">
+    <row r="591" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P591" s="2"/>
       <c r="S591" s="2"/>
     </row>
-    <row r="592">
+    <row r="592" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P592" s="2"/>
       <c r="S592" s="2"/>
     </row>
-    <row r="593">
+    <row r="593" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P593" s="2"/>
       <c r="S593" s="2"/>
     </row>
-    <row r="594">
+    <row r="594" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P594" s="2"/>
       <c r="S594" s="2"/>
     </row>
-    <row r="595">
+    <row r="595" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P595" s="2"/>
       <c r="S595" s="2"/>
     </row>
-    <row r="596">
+    <row r="596" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P596" s="2"/>
       <c r="S596" s="2"/>
     </row>
-    <row r="597">
+    <row r="597" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P597" s="2"/>
       <c r="S597" s="2"/>
     </row>
-    <row r="598">
+    <row r="598" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P598" s="2"/>
       <c r="S598" s="2"/>
     </row>
-    <row r="599">
+    <row r="599" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P599" s="2"/>
       <c r="S599" s="2"/>
     </row>
-    <row r="600">
+    <row r="600" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P600" s="2"/>
       <c r="S600" s="2"/>
     </row>
-    <row r="601">
+    <row r="601" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P601" s="2"/>
       <c r="S601" s="2"/>
     </row>
-    <row r="602">
+    <row r="602" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P602" s="2"/>
       <c r="S602" s="2"/>
     </row>
-    <row r="603">
+    <row r="603" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P603" s="2"/>
       <c r="S603" s="2"/>
     </row>
-    <row r="604">
+    <row r="604" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P604" s="2"/>
       <c r="S604" s="2"/>
     </row>
-    <row r="605">
+    <row r="605" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P605" s="2"/>
       <c r="S605" s="2"/>
     </row>
-    <row r="606">
+    <row r="606" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P606" s="2"/>
       <c r="S606" s="2"/>
     </row>
-    <row r="607">
+    <row r="607" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P607" s="2"/>
       <c r="S607" s="2"/>
     </row>
-    <row r="608">
+    <row r="608" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P608" s="2"/>
       <c r="S608" s="2"/>
     </row>
-    <row r="609">
+    <row r="609" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P609" s="2"/>
       <c r="S609" s="2"/>
     </row>
-    <row r="610">
+    <row r="610" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P610" s="2"/>
       <c r="S610" s="2"/>
     </row>
-    <row r="611">
+    <row r="611" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P611" s="2"/>
       <c r="S611" s="2"/>
     </row>
-    <row r="612">
+    <row r="612" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P612" s="2"/>
       <c r="S612" s="2"/>
     </row>
-    <row r="613">
+    <row r="613" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P613" s="2"/>
       <c r="S613" s="2"/>
     </row>
-    <row r="614">
+    <row r="614" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P614" s="2"/>
       <c r="S614" s="2"/>
     </row>
-    <row r="615">
+    <row r="615" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P615" s="2"/>
       <c r="S615" s="2"/>
     </row>
-    <row r="616">
+    <row r="616" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P616" s="2"/>
       <c r="S616" s="2"/>
     </row>
-    <row r="617">
+    <row r="617" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P617" s="2"/>
       <c r="S617" s="2"/>
     </row>
-    <row r="618">
+    <row r="618" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P618" s="2"/>
       <c r="S618" s="2"/>
     </row>
-    <row r="619">
+    <row r="619" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P619" s="2"/>
       <c r="S619" s="2"/>
     </row>
-    <row r="620">
+    <row r="620" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P620" s="2"/>
       <c r="S620" s="2"/>
     </row>
-    <row r="621">
+    <row r="621" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P621" s="2"/>
       <c r="S621" s="2"/>
     </row>
-    <row r="622">
+    <row r="622" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P622" s="2"/>
       <c r="S622" s="2"/>
     </row>
-    <row r="623">
+    <row r="623" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P623" s="2"/>
       <c r="S623" s="2"/>
     </row>
-    <row r="624">
+    <row r="624" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P624" s="2"/>
       <c r="S624" s="2"/>
     </row>
-    <row r="625">
+    <row r="625" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P625" s="2"/>
       <c r="S625" s="2"/>
     </row>
-    <row r="626">
+    <row r="626" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P626" s="2"/>
       <c r="S626" s="2"/>
     </row>
-    <row r="627">
+    <row r="627" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P627" s="2"/>
       <c r="S627" s="2"/>
     </row>
-    <row r="628">
+    <row r="628" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P628" s="2"/>
       <c r="S628" s="2"/>
     </row>
-    <row r="629">
+    <row r="629" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P629" s="2"/>
       <c r="S629" s="2"/>
     </row>
-    <row r="630">
+    <row r="630" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P630" s="2"/>
       <c r="S630" s="2"/>
     </row>
-    <row r="631">
+    <row r="631" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P631" s="2"/>
       <c r="S631" s="2"/>
     </row>
-    <row r="632">
+    <row r="632" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P632" s="2"/>
       <c r="S632" s="2"/>
     </row>
-    <row r="633">
+    <row r="633" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P633" s="2"/>
       <c r="S633" s="2"/>
     </row>
-    <row r="634">
+    <row r="634" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P634" s="2"/>
       <c r="S634" s="2"/>
     </row>
-    <row r="635">
+    <row r="635" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P635" s="2"/>
       <c r="S635" s="2"/>
     </row>
-    <row r="636">
+    <row r="636" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P636" s="2"/>
       <c r="S636" s="2"/>
     </row>
-    <row r="637">
+    <row r="637" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P637" s="2"/>
       <c r="S637" s="2"/>
     </row>
-    <row r="638">
+    <row r="638" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P638" s="2"/>
       <c r="S638" s="2"/>
     </row>
-    <row r="639">
+    <row r="639" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P639" s="2"/>
       <c r="S639" s="2"/>
     </row>
-    <row r="640">
+    <row r="640" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P640" s="2"/>
       <c r="S640" s="2"/>
     </row>
-    <row r="641">
+    <row r="641" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P641" s="2"/>
       <c r="S641" s="2"/>
     </row>
-    <row r="642">
+    <row r="642" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P642" s="2"/>
       <c r="S642" s="2"/>
     </row>
-    <row r="643">
+    <row r="643" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P643" s="2"/>
       <c r="S643" s="2"/>
     </row>
-    <row r="644">
+    <row r="644" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P644" s="2"/>
       <c r="S644" s="2"/>
     </row>
-    <row r="645">
+    <row r="645" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P645" s="2"/>
       <c r="S645" s="2"/>
     </row>
-    <row r="646">
+    <row r="646" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P646" s="2"/>
       <c r="S646" s="2"/>
     </row>
-    <row r="647">
+    <row r="647" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P647" s="2"/>
       <c r="S647" s="2"/>
     </row>
-    <row r="648">
+    <row r="648" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P648" s="2"/>
       <c r="S648" s="2"/>
     </row>
-    <row r="649">
+    <row r="649" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P649" s="2"/>
       <c r="S649" s="2"/>
     </row>
-    <row r="650">
+    <row r="650" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P650" s="2"/>
       <c r="S650" s="2"/>
     </row>
-    <row r="651">
+    <row r="651" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P651" s="2"/>
       <c r="S651" s="2"/>
     </row>
-    <row r="652">
+    <row r="652" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P652" s="2"/>
       <c r="S652" s="2"/>
     </row>
-    <row r="653">
+    <row r="653" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P653" s="2"/>
       <c r="S653" s="2"/>
     </row>
-    <row r="654">
+    <row r="654" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P654" s="2"/>
       <c r="S654" s="2"/>
     </row>
-    <row r="655">
+    <row r="655" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P655" s="2"/>
       <c r="S655" s="2"/>
     </row>
-    <row r="656">
+    <row r="656" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P656" s="2"/>
       <c r="S656" s="2"/>
     </row>
-    <row r="657">
+    <row r="657" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P657" s="2"/>
       <c r="S657" s="2"/>
     </row>
-    <row r="658">
+    <row r="658" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P658" s="2"/>
       <c r="S658" s="2"/>
     </row>
-    <row r="659">
+    <row r="659" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P659" s="2"/>
       <c r="S659" s="2"/>
     </row>
-    <row r="660">
+    <row r="660" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P660" s="2"/>
       <c r="S660" s="2"/>
     </row>
-    <row r="661">
+    <row r="661" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P661" s="2"/>
       <c r="S661" s="2"/>
     </row>
-    <row r="662">
+    <row r="662" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P662" s="2"/>
       <c r="S662" s="2"/>
     </row>
-    <row r="663">
+    <row r="663" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P663" s="2"/>
       <c r="S663" s="2"/>
     </row>
-    <row r="664">
+    <row r="664" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P664" s="2"/>
       <c r="S664" s="2"/>
     </row>
-    <row r="665">
+    <row r="665" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P665" s="2"/>
       <c r="S665" s="2"/>
     </row>
-    <row r="666">
+    <row r="666" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P666" s="2"/>
       <c r="S666" s="2"/>
     </row>
-    <row r="667">
+    <row r="667" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P667" s="2"/>
       <c r="S667" s="2"/>
     </row>
-    <row r="668">
+    <row r="668" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P668" s="2"/>
       <c r="S668" s="2"/>
     </row>
-    <row r="669">
+    <row r="669" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P669" s="2"/>
       <c r="S669" s="2"/>
     </row>
-    <row r="670">
+    <row r="670" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P670" s="2"/>
       <c r="S670" s="2"/>
     </row>
-    <row r="671">
+    <row r="671" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P671" s="2"/>
       <c r="S671" s="2"/>
     </row>
-    <row r="672">
+    <row r="672" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P672" s="2"/>
       <c r="S672" s="2"/>
     </row>
-    <row r="673">
+    <row r="673" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P673" s="2"/>
       <c r="S673" s="2"/>
     </row>
-    <row r="674">
+    <row r="674" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P674" s="2"/>
       <c r="S674" s="2"/>
     </row>
-    <row r="675">
+    <row r="675" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P675" s="2"/>
       <c r="S675" s="2"/>
     </row>
-    <row r="676">
+    <row r="676" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P676" s="2"/>
       <c r="S676" s="2"/>
     </row>
-    <row r="677">
+    <row r="677" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P677" s="2"/>
       <c r="S677" s="2"/>
     </row>
-    <row r="678">
+    <row r="678" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P678" s="2"/>
       <c r="S678" s="2"/>
     </row>
-    <row r="679">
+    <row r="679" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P679" s="2"/>
       <c r="S679" s="2"/>
     </row>
-    <row r="680">
+    <row r="680" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P680" s="2"/>
       <c r="S680" s="2"/>
     </row>
-    <row r="681">
+    <row r="681" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P681" s="2"/>
       <c r="S681" s="2"/>
     </row>
-    <row r="682">
+    <row r="682" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P682" s="2"/>
       <c r="S682" s="2"/>
     </row>
-    <row r="683">
+    <row r="683" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P683" s="2"/>
       <c r="S683" s="2"/>
     </row>
-    <row r="684">
+    <row r="684" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P684" s="2"/>
       <c r="S684" s="2"/>
     </row>
-    <row r="685">
+    <row r="685" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P685" s="2"/>
       <c r="S685" s="2"/>
     </row>
-    <row r="686">
+    <row r="686" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P686" s="2"/>
       <c r="S686" s="2"/>
     </row>
-    <row r="687">
+    <row r="687" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P687" s="2"/>
       <c r="S687" s="2"/>
     </row>
-    <row r="688">
+    <row r="688" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P688" s="2"/>
       <c r="S688" s="2"/>
     </row>
-    <row r="689">
+    <row r="689" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P689" s="2"/>
       <c r="S689" s="2"/>
     </row>
-    <row r="690">
+    <row r="690" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P690" s="2"/>
       <c r="S690" s="2"/>
     </row>
-    <row r="691">
+    <row r="691" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P691" s="2"/>
       <c r="S691" s="2"/>
     </row>
-    <row r="692">
+    <row r="692" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P692" s="2"/>
       <c r="S692" s="2"/>
     </row>
-    <row r="693">
+    <row r="693" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P693" s="2"/>
       <c r="S693" s="2"/>
     </row>
-    <row r="694">
+    <row r="694" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P694" s="2"/>
       <c r="S694" s="2"/>
     </row>
-    <row r="695">
+    <row r="695" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P695" s="2"/>
       <c r="S695" s="2"/>
     </row>
-    <row r="696">
+    <row r="696" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P696" s="2"/>
       <c r="S696" s="2"/>
     </row>
-    <row r="697">
+    <row r="697" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P697" s="2"/>
       <c r="S697" s="2"/>
     </row>
-    <row r="698">
+    <row r="698" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P698" s="2"/>
       <c r="S698" s="2"/>
     </row>
-    <row r="699">
+    <row r="699" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P699" s="2"/>
       <c r="S699" s="2"/>
     </row>
-    <row r="700">
+    <row r="700" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P700" s="2"/>
       <c r="S700" s="2"/>
     </row>
-    <row r="701">
+    <row r="701" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P701" s="2"/>
       <c r="S701" s="2"/>
     </row>
-    <row r="702">
+    <row r="702" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P702" s="2"/>
       <c r="S702" s="2"/>
     </row>
-    <row r="703">
+    <row r="703" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P703" s="2"/>
       <c r="S703" s="2"/>
     </row>
-    <row r="704">
+    <row r="704" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P704" s="2"/>
       <c r="S704" s="2"/>
     </row>
-    <row r="705">
+    <row r="705" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P705" s="2"/>
       <c r="S705" s="2"/>
     </row>
-    <row r="706">
+    <row r="706" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P706" s="2"/>
       <c r="S706" s="2"/>
     </row>
-    <row r="707">
+    <row r="707" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P707" s="2"/>
       <c r="S707" s="2"/>
     </row>
-    <row r="708">
+    <row r="708" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P708" s="2"/>
       <c r="S708" s="2"/>
     </row>
-    <row r="709">
+    <row r="709" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P709" s="2"/>
       <c r="S709" s="2"/>
     </row>
-    <row r="710">
+    <row r="710" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P710" s="2"/>
       <c r="S710" s="2"/>
     </row>
-    <row r="711">
+    <row r="711" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P711" s="2"/>
       <c r="S711" s="2"/>
     </row>
-    <row r="712">
+    <row r="712" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P712" s="2"/>
       <c r="S712" s="2"/>
     </row>
-    <row r="713">
+    <row r="713" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P713" s="2"/>
       <c r="S713" s="2"/>
     </row>
-    <row r="714">
+    <row r="714" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P714" s="2"/>
       <c r="S714" s="2"/>
     </row>
-    <row r="715">
+    <row r="715" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P715" s="2"/>
       <c r="S715" s="2"/>
     </row>
-    <row r="716">
+    <row r="716" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P716" s="2"/>
       <c r="S716" s="2"/>
     </row>
-    <row r="717">
+    <row r="717" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P717" s="2"/>
       <c r="S717" s="2"/>
     </row>
-    <row r="718">
+    <row r="718" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P718" s="2"/>
       <c r="S718" s="2"/>
     </row>
-    <row r="719">
+    <row r="719" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P719" s="2"/>
       <c r="S719" s="2"/>
     </row>
-    <row r="720">
+    <row r="720" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P720" s="2"/>
       <c r="S720" s="2"/>
     </row>
-    <row r="721">
+    <row r="721" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P721" s="2"/>
       <c r="S721" s="2"/>
     </row>
-    <row r="722">
+    <row r="722" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P722" s="2"/>
       <c r="S722" s="2"/>
     </row>
-    <row r="723">
+    <row r="723" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P723" s="2"/>
       <c r="S723" s="2"/>
     </row>
-    <row r="724">
+    <row r="724" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P724" s="2"/>
       <c r="S724" s="2"/>
     </row>
-    <row r="725">
+    <row r="725" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P725" s="2"/>
       <c r="S725" s="2"/>
     </row>
-    <row r="726">
+    <row r="726" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P726" s="2"/>
       <c r="S726" s="2"/>
     </row>
-    <row r="727">
+    <row r="727" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P727" s="2"/>
       <c r="S727" s="2"/>
     </row>
-    <row r="728">
+    <row r="728" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P728" s="2"/>
       <c r="S728" s="2"/>
     </row>
-    <row r="729">
+    <row r="729" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P729" s="2"/>
       <c r="S729" s="2"/>
     </row>
-    <row r="730">
+    <row r="730" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P730" s="2"/>
       <c r="S730" s="2"/>
     </row>
-    <row r="731">
+    <row r="731" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P731" s="2"/>
       <c r="S731" s="2"/>
     </row>
-    <row r="732">
+    <row r="732" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P732" s="2"/>
       <c r="S732" s="2"/>
     </row>
-    <row r="733">
+    <row r="733" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P733" s="2"/>
       <c r="S733" s="2"/>
     </row>
-    <row r="734">
+    <row r="734" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P734" s="2"/>
       <c r="S734" s="2"/>
     </row>
-    <row r="735">
+    <row r="735" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P735" s="2"/>
       <c r="S735" s="2"/>
     </row>
-    <row r="736">
+    <row r="736" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P736" s="2"/>
       <c r="S736" s="2"/>
     </row>
-    <row r="737">
+    <row r="737" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P737" s="2"/>
       <c r="S737" s="2"/>
     </row>
-    <row r="738">
+    <row r="738" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P738" s="2"/>
       <c r="S738" s="2"/>
     </row>
-    <row r="739">
+    <row r="739" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P739" s="2"/>
       <c r="S739" s="2"/>
     </row>
-    <row r="740">
+    <row r="740" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P740" s="2"/>
       <c r="S740" s="2"/>
     </row>
-    <row r="741">
+    <row r="741" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P741" s="2"/>
       <c r="S741" s="2"/>
     </row>
-    <row r="742">
+    <row r="742" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P742" s="2"/>
       <c r="S742" s="2"/>
     </row>
-    <row r="743">
+    <row r="743" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P743" s="2"/>
       <c r="S743" s="2"/>
     </row>
-    <row r="744">
+    <row r="744" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P744" s="2"/>
       <c r="S744" s="2"/>
     </row>
-    <row r="745">
+    <row r="745" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P745" s="2"/>
       <c r="S745" s="2"/>
     </row>
-    <row r="746">
+    <row r="746" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P746" s="2"/>
       <c r="S746" s="2"/>
     </row>
-    <row r="747">
+    <row r="747" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P747" s="2"/>
       <c r="S747" s="2"/>
     </row>
-    <row r="748">
+    <row r="748" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P748" s="2"/>
       <c r="S748" s="2"/>
     </row>
-    <row r="749">
+    <row r="749" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P749" s="2"/>
       <c r="S749" s="2"/>
     </row>
-    <row r="750">
+    <row r="750" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P750" s="2"/>
       <c r="S750" s="2"/>
     </row>
-    <row r="751">
+    <row r="751" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P751" s="2"/>
       <c r="S751" s="2"/>
     </row>
-    <row r="752">
+    <row r="752" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P752" s="2"/>
       <c r="S752" s="2"/>
     </row>
-    <row r="753">
+    <row r="753" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P753" s="2"/>
       <c r="S753" s="2"/>
     </row>
-    <row r="754">
+    <row r="754" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P754" s="2"/>
       <c r="S754" s="2"/>
     </row>
-    <row r="755">
+    <row r="755" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P755" s="2"/>
       <c r="S755" s="2"/>
     </row>
-    <row r="756">
+    <row r="756" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P756" s="2"/>
       <c r="S756" s="2"/>
     </row>
-    <row r="757">
+    <row r="757" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P757" s="2"/>
       <c r="S757" s="2"/>
     </row>
-    <row r="758">
+    <row r="758" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P758" s="2"/>
       <c r="S758" s="2"/>
     </row>
-    <row r="759">
+    <row r="759" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P759" s="2"/>
       <c r="S759" s="2"/>
     </row>
-    <row r="760">
+    <row r="760" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P760" s="2"/>
       <c r="S760" s="2"/>
     </row>
-    <row r="761">
+    <row r="761" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P761" s="2"/>
       <c r="S761" s="2"/>
     </row>
-    <row r="762">
+    <row r="762" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P762" s="2"/>
       <c r="S762" s="2"/>
     </row>
-    <row r="763">
+    <row r="763" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P763" s="2"/>
       <c r="S763" s="2"/>
     </row>
-    <row r="764">
+    <row r="764" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P764" s="2"/>
       <c r="S764" s="2"/>
     </row>
-    <row r="765">
+    <row r="765" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P765" s="2"/>
       <c r="S765" s="2"/>
     </row>
-    <row r="766">
+    <row r="766" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P766" s="2"/>
       <c r="S766" s="2"/>
     </row>
-    <row r="767">
+    <row r="767" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P767" s="2"/>
       <c r="S767" s="2"/>
     </row>
-    <row r="768">
+    <row r="768" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P768" s="2"/>
       <c r="S768" s="2"/>
     </row>
-    <row r="769">
+    <row r="769" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P769" s="2"/>
       <c r="S769" s="2"/>
     </row>
-    <row r="770">
+    <row r="770" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P770" s="2"/>
       <c r="S770" s="2"/>
     </row>
-    <row r="771">
+    <row r="771" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P771" s="2"/>
       <c r="S771" s="2"/>
     </row>
-    <row r="772">
+    <row r="772" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P772" s="2"/>
       <c r="S772" s="2"/>
     </row>
-    <row r="773">
+    <row r="773" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P773" s="2"/>
       <c r="S773" s="2"/>
     </row>
-    <row r="774">
+    <row r="774" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P774" s="2"/>
       <c r="S774" s="2"/>
     </row>
-    <row r="775">
+    <row r="775" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P775" s="2"/>
       <c r="S775" s="2"/>
     </row>
-    <row r="776">
+    <row r="776" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P776" s="2"/>
       <c r="S776" s="2"/>
     </row>
-    <row r="777">
+    <row r="777" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P777" s="2"/>
       <c r="S777" s="2"/>
     </row>
-    <row r="778">
+    <row r="778" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P778" s="2"/>
       <c r="S778" s="2"/>
     </row>
-    <row r="779">
+    <row r="779" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P779" s="2"/>
       <c r="S779" s="2"/>
     </row>
-    <row r="780">
+    <row r="780" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P780" s="2"/>
       <c r="S780" s="2"/>
     </row>
-    <row r="781">
+    <row r="781" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P781" s="2"/>
       <c r="S781" s="2"/>
     </row>
-    <row r="782">
+    <row r="782" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P782" s="2"/>
       <c r="S782" s="2"/>
     </row>
-    <row r="783">
+    <row r="783" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P783" s="2"/>
       <c r="S783" s="2"/>
     </row>
-    <row r="784">
+    <row r="784" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P784" s="2"/>
       <c r="S784" s="2"/>
     </row>
-    <row r="785">
+    <row r="785" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P785" s="2"/>
       <c r="S785" s="2"/>
     </row>
-    <row r="786">
+    <row r="786" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P786" s="2"/>
       <c r="S786" s="2"/>
     </row>
-    <row r="787">
+    <row r="787" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P787" s="2"/>
       <c r="S787" s="2"/>
     </row>
-    <row r="788">
+    <row r="788" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P788" s="2"/>
       <c r="S788" s="2"/>
     </row>
-    <row r="789">
+    <row r="789" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P789" s="2"/>
       <c r="S789" s="2"/>
     </row>
-    <row r="790">
+    <row r="790" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P790" s="2"/>
       <c r="S790" s="2"/>
     </row>
-    <row r="791">
+    <row r="791" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P791" s="2"/>
       <c r="S791" s="2"/>
     </row>
-    <row r="792">
+    <row r="792" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P792" s="2"/>
       <c r="S792" s="2"/>
     </row>
-    <row r="793">
+    <row r="793" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P793" s="2"/>
       <c r="S793" s="2"/>
     </row>
-    <row r="794">
+    <row r="794" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P794" s="2"/>
       <c r="S794" s="2"/>
     </row>
-    <row r="795">
+    <row r="795" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P795" s="2"/>
       <c r="S795" s="2"/>
     </row>
-    <row r="796">
+    <row r="796" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P796" s="2"/>
       <c r="S796" s="2"/>
     </row>
-    <row r="797">
+    <row r="797" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P797" s="2"/>
       <c r="S797" s="2"/>
     </row>
-    <row r="798">
+    <row r="798" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P798" s="2"/>
       <c r="S798" s="2"/>
     </row>
-    <row r="799">
+    <row r="799" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P799" s="2"/>
       <c r="S799" s="2"/>
     </row>
-    <row r="800">
+    <row r="800" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P800" s="2"/>
       <c r="S800" s="2"/>
     </row>
-    <row r="801">
+    <row r="801" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P801" s="2"/>
       <c r="S801" s="2"/>
     </row>
-    <row r="802">
+    <row r="802" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P802" s="2"/>
       <c r="S802" s="2"/>
     </row>
-    <row r="803">
+    <row r="803" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P803" s="2"/>
       <c r="S803" s="2"/>
     </row>
-    <row r="804">
+    <row r="804" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P804" s="2"/>
       <c r="S804" s="2"/>
     </row>
-    <row r="805">
+    <row r="805" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P805" s="2"/>
       <c r="S805" s="2"/>
     </row>
-    <row r="806">
+    <row r="806" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P806" s="2"/>
       <c r="S806" s="2"/>
     </row>
-    <row r="807">
+    <row r="807" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P807" s="2"/>
       <c r="S807" s="2"/>
     </row>
-    <row r="808">
+    <row r="808" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P808" s="2"/>
       <c r="S808" s="2"/>
     </row>
-    <row r="809">
+    <row r="809" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P809" s="2"/>
       <c r="S809" s="2"/>
     </row>
-    <row r="810">
+    <row r="810" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P810" s="2"/>
       <c r="S810" s="2"/>
     </row>
-    <row r="811">
+    <row r="811" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P811" s="2"/>
       <c r="S811" s="2"/>
     </row>
-    <row r="812">
+    <row r="812" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P812" s="2"/>
       <c r="S812" s="2"/>
     </row>
-    <row r="813">
+    <row r="813" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P813" s="2"/>
       <c r="S813" s="2"/>
     </row>
-    <row r="814">
+    <row r="814" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P814" s="2"/>
       <c r="S814" s="2"/>
     </row>
-    <row r="815">
+    <row r="815" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P815" s="2"/>
       <c r="S815" s="2"/>
     </row>
-    <row r="816">
+    <row r="816" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P816" s="2"/>
       <c r="S816" s="2"/>
     </row>
-    <row r="817">
+    <row r="817" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P817" s="2"/>
       <c r="S817" s="2"/>
     </row>
-    <row r="818">
+    <row r="818" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P818" s="2"/>
       <c r="S818" s="2"/>
     </row>
-    <row r="819">
+    <row r="819" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P819" s="2"/>
       <c r="S819" s="2"/>
     </row>
-    <row r="820">
+    <row r="820" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P820" s="2"/>
       <c r="S820" s="2"/>
     </row>
-    <row r="821">
+    <row r="821" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P821" s="2"/>
       <c r="S821" s="2"/>
     </row>
-    <row r="822">
+    <row r="822" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P822" s="2"/>
       <c r="S822" s="2"/>
     </row>
-    <row r="823">
+    <row r="823" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P823" s="2"/>
       <c r="S823" s="2"/>
     </row>
-    <row r="824">
+    <row r="824" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P824" s="2"/>
       <c r="S824" s="2"/>
     </row>
-    <row r="825">
+    <row r="825" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P825" s="2"/>
       <c r="S825" s="2"/>
     </row>
-    <row r="826">
+    <row r="826" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P826" s="2"/>
       <c r="S826" s="2"/>
     </row>
-    <row r="827">
+    <row r="827" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P827" s="2"/>
       <c r="S827" s="2"/>
     </row>
-    <row r="828">
+    <row r="828" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P828" s="2"/>
       <c r="S828" s="2"/>
     </row>
-    <row r="829">
+    <row r="829" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P829" s="2"/>
       <c r="S829" s="2"/>
     </row>
-    <row r="830">
+    <row r="830" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P830" s="2"/>
       <c r="S830" s="2"/>
     </row>
-    <row r="831">
+    <row r="831" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P831" s="2"/>
       <c r="S831" s="2"/>
     </row>
-    <row r="832">
+    <row r="832" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P832" s="2"/>
       <c r="S832" s="2"/>
     </row>
-    <row r="833">
+    <row r="833" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P833" s="2"/>
       <c r="S833" s="2"/>
     </row>
-    <row r="834">
+    <row r="834" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P834" s="2"/>
       <c r="S834" s="2"/>
     </row>
-    <row r="835">
+    <row r="835" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P835" s="2"/>
       <c r="S835" s="2"/>
     </row>
-    <row r="836">
+    <row r="836" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P836" s="2"/>
       <c r="S836" s="2"/>
     </row>
-    <row r="837">
+    <row r="837" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P837" s="2"/>
       <c r="S837" s="2"/>
     </row>
-    <row r="838">
+    <row r="838" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P838" s="2"/>
       <c r="S838" s="2"/>
     </row>
-    <row r="839">
+    <row r="839" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P839" s="2"/>
       <c r="S839" s="2"/>
     </row>
-    <row r="840">
+    <row r="840" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P840" s="2"/>
       <c r="S840" s="2"/>
     </row>
-    <row r="841">
+    <row r="841" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P841" s="2"/>
       <c r="S841" s="2"/>
     </row>
-    <row r="842">
+    <row r="842" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P842" s="2"/>
       <c r="S842" s="2"/>
     </row>
-    <row r="843">
+    <row r="843" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P843" s="2"/>
       <c r="S843" s="2"/>
     </row>
-    <row r="844">
+    <row r="844" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P844" s="2"/>
       <c r="S844" s="2"/>
     </row>
-    <row r="845">
+    <row r="845" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P845" s="2"/>
       <c r="S845" s="2"/>
     </row>
-    <row r="846">
+    <row r="846" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P846" s="2"/>
       <c r="S846" s="2"/>
     </row>
-    <row r="847">
+    <row r="847" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P847" s="2"/>
       <c r="S847" s="2"/>
     </row>
-    <row r="848">
+    <row r="848" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P848" s="2"/>
       <c r="S848" s="2"/>
     </row>
-    <row r="849">
+    <row r="849" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P849" s="2"/>
       <c r="S849" s="2"/>
     </row>
-    <row r="850">
+    <row r="850" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P850" s="2"/>
       <c r="S850" s="2"/>
     </row>
-    <row r="851">
+    <row r="851" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P851" s="2"/>
       <c r="S851" s="2"/>
     </row>
-    <row r="852">
+    <row r="852" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P852" s="2"/>
       <c r="S852" s="2"/>
     </row>
-    <row r="853">
+    <row r="853" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P853" s="2"/>
       <c r="S853" s="2"/>
     </row>
-    <row r="854">
+    <row r="854" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P854" s="2"/>
       <c r="S854" s="2"/>
     </row>
-    <row r="855">
+    <row r="855" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P855" s="2"/>
       <c r="S855" s="2"/>
     </row>
-    <row r="856">
+    <row r="856" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P856" s="2"/>
       <c r="S856" s="2"/>
     </row>
-    <row r="857">
+    <row r="857" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P857" s="2"/>
       <c r="S857" s="2"/>
     </row>
-    <row r="858">
+    <row r="858" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P858" s="2"/>
       <c r="S858" s="2"/>
     </row>
-    <row r="859">
+    <row r="859" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P859" s="2"/>
       <c r="S859" s="2"/>
     </row>
-    <row r="860">
+    <row r="860" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P860" s="2"/>
       <c r="S860" s="2"/>
     </row>
-    <row r="861">
+    <row r="861" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P861" s="2"/>
       <c r="S861" s="2"/>
     </row>
-    <row r="862">
+    <row r="862" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P862" s="2"/>
       <c r="S862" s="2"/>
     </row>
-    <row r="863">
+    <row r="863" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P863" s="2"/>
       <c r="S863" s="2"/>
     </row>
-    <row r="864">
+    <row r="864" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P864" s="2"/>
       <c r="S864" s="2"/>
     </row>
-    <row r="865">
+    <row r="865" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P865" s="2"/>
       <c r="S865" s="2"/>
     </row>
-    <row r="866">
+    <row r="866" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P866" s="2"/>
       <c r="S866" s="2"/>
     </row>
-    <row r="867">
+    <row r="867" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P867" s="2"/>
       <c r="S867" s="2"/>
     </row>
-    <row r="868">
+    <row r="868" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P868" s="2"/>
       <c r="S868" s="2"/>
     </row>
-    <row r="869">
+    <row r="869" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P869" s="2"/>
       <c r="S869" s="2"/>
     </row>
-    <row r="870">
+    <row r="870" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P870" s="2"/>
       <c r="S870" s="2"/>
     </row>
-    <row r="871">
+    <row r="871" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P871" s="2"/>
       <c r="S871" s="2"/>
     </row>
-    <row r="872">
+    <row r="872" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P872" s="2"/>
       <c r="S872" s="2"/>
     </row>
-    <row r="873">
+    <row r="873" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P873" s="2"/>
       <c r="S873" s="2"/>
     </row>
-    <row r="874">
+    <row r="874" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P874" s="2"/>
       <c r="S874" s="2"/>
     </row>
-    <row r="875">
+    <row r="875" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P875" s="2"/>
       <c r="S875" s="2"/>
     </row>
-    <row r="876">
+    <row r="876" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P876" s="2"/>
       <c r="S876" s="2"/>
     </row>
-    <row r="877">
+    <row r="877" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P877" s="2"/>
       <c r="S877" s="2"/>
     </row>
-    <row r="878">
+    <row r="878" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P878" s="2"/>
       <c r="S878" s="2"/>
     </row>
-    <row r="879">
+    <row r="879" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P879" s="2"/>
       <c r="S879" s="2"/>
     </row>
-    <row r="880">
+    <row r="880" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P880" s="2"/>
       <c r="S880" s="2"/>
     </row>
-    <row r="881">
+    <row r="881" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P881" s="2"/>
       <c r="S881" s="2"/>
     </row>
-    <row r="882">
+    <row r="882" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P882" s="2"/>
       <c r="S882" s="2"/>
     </row>
-    <row r="883">
+    <row r="883" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P883" s="2"/>
       <c r="S883" s="2"/>
     </row>
-    <row r="884">
+    <row r="884" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P884" s="2"/>
       <c r="S884" s="2"/>
     </row>
-    <row r="885">
+    <row r="885" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P885" s="2"/>
       <c r="S885" s="2"/>
     </row>
-    <row r="886">
+    <row r="886" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P886" s="2"/>
       <c r="S886" s="2"/>
     </row>
-    <row r="887">
+    <row r="887" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P887" s="2"/>
       <c r="S887" s="2"/>
     </row>
-    <row r="888">
+    <row r="888" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P888" s="2"/>
       <c r="S888" s="2"/>
     </row>
-    <row r="889">
+    <row r="889" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P889" s="2"/>
       <c r="S889" s="2"/>
     </row>
-    <row r="890">
+    <row r="890" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P890" s="2"/>
       <c r="S890" s="2"/>
     </row>
-    <row r="891">
+    <row r="891" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P891" s="2"/>
       <c r="S891" s="2"/>
     </row>
-    <row r="892">
+    <row r="892" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P892" s="2"/>
       <c r="S892" s="2"/>
     </row>
-    <row r="893">
+    <row r="893" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P893" s="2"/>
       <c r="S893" s="2"/>
     </row>
-    <row r="894">
+    <row r="894" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P894" s="2"/>
       <c r="S894" s="2"/>
     </row>
-    <row r="895">
+    <row r="895" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P895" s="2"/>
       <c r="S895" s="2"/>
     </row>
-    <row r="896">
+    <row r="896" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P896" s="2"/>
       <c r="S896" s="2"/>
     </row>
-    <row r="897">
+    <row r="897" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P897" s="2"/>
       <c r="S897" s="2"/>
     </row>
-    <row r="898">
+    <row r="898" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P898" s="2"/>
       <c r="S898" s="2"/>
     </row>
-    <row r="899">
+    <row r="899" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P899" s="2"/>
       <c r="S899" s="2"/>
     </row>
-    <row r="900">
+    <row r="900" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P900" s="2"/>
       <c r="S900" s="2"/>
     </row>
-    <row r="901">
+    <row r="901" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P901" s="2"/>
       <c r="S901" s="2"/>
     </row>
-    <row r="902">
+    <row r="902" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P902" s="2"/>
       <c r="S902" s="2"/>
     </row>
-    <row r="903">
+    <row r="903" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P903" s="2"/>
       <c r="S903" s="2"/>
     </row>
-    <row r="904">
+    <row r="904" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P904" s="2"/>
       <c r="S904" s="2"/>
     </row>
-    <row r="905">
+    <row r="905" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P905" s="2"/>
       <c r="S905" s="2"/>
     </row>
-    <row r="906">
+    <row r="906" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P906" s="2"/>
       <c r="S906" s="2"/>
     </row>
-    <row r="907">
+    <row r="907" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P907" s="2"/>
       <c r="S907" s="2"/>
     </row>
-    <row r="908">
+    <row r="908" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P908" s="2"/>
       <c r="S908" s="2"/>
     </row>
-    <row r="909">
+    <row r="909" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P909" s="2"/>
       <c r="S909" s="2"/>
     </row>
-    <row r="910">
+    <row r="910" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P910" s="2"/>
       <c r="S910" s="2"/>
     </row>
-    <row r="911">
+    <row r="911" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P911" s="2"/>
       <c r="S911" s="2"/>
     </row>
-    <row r="912">
+    <row r="912" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P912" s="2"/>
       <c r="S912" s="2"/>
     </row>
-    <row r="913">
+    <row r="913" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P913" s="2"/>
       <c r="S913" s="2"/>
     </row>
-    <row r="914">
+    <row r="914" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P914" s="2"/>
       <c r="S914" s="2"/>
     </row>
-    <row r="915">
+    <row r="915" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P915" s="2"/>
       <c r="S915" s="2"/>
     </row>
-    <row r="916">
+    <row r="916" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P916" s="2"/>
       <c r="S916" s="2"/>
     </row>
-    <row r="917">
+    <row r="917" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P917" s="2"/>
       <c r="S917" s="2"/>
     </row>
-    <row r="918">
+    <row r="918" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P918" s="2"/>
       <c r="S918" s="2"/>
     </row>
-    <row r="919">
+    <row r="919" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P919" s="2"/>
       <c r="S919" s="2"/>
     </row>
-    <row r="920">
+    <row r="920" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P920" s="2"/>
       <c r="S920" s="2"/>
     </row>
-    <row r="921">
+    <row r="921" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P921" s="2"/>
       <c r="S921" s="2"/>
     </row>
-    <row r="922">
+    <row r="922" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P922" s="2"/>
       <c r="S922" s="2"/>
     </row>
-    <row r="923">
+    <row r="923" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P923" s="2"/>
       <c r="S923" s="2"/>
     </row>
-    <row r="924">
+    <row r="924" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P924" s="2"/>
       <c r="S924" s="2"/>
     </row>
-    <row r="925">
+    <row r="925" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P925" s="2"/>
       <c r="S925" s="2"/>
     </row>
-    <row r="926">
+    <row r="926" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P926" s="2"/>
       <c r="S926" s="2"/>
     </row>
-    <row r="927">
+    <row r="927" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P927" s="2"/>
       <c r="S927" s="2"/>
     </row>
-    <row r="928">
+    <row r="928" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P928" s="2"/>
       <c r="S928" s="2"/>
     </row>
-    <row r="929">
+    <row r="929" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P929" s="2"/>
       <c r="S929" s="2"/>
     </row>
-    <row r="930">
+    <row r="930" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P930" s="2"/>
       <c r="S930" s="2"/>
     </row>
-    <row r="931">
+    <row r="931" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P931" s="2"/>
       <c r="S931" s="2"/>
     </row>
-    <row r="932">
+    <row r="932" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P932" s="2"/>
       <c r="S932" s="2"/>
     </row>
-    <row r="933">
+    <row r="933" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P933" s="2"/>
       <c r="S933" s="2"/>
     </row>
-    <row r="934">
+    <row r="934" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P934" s="2"/>
       <c r="S934" s="2"/>
     </row>
-    <row r="935">
+    <row r="935" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P935" s="2"/>
       <c r="S935" s="2"/>
     </row>
-    <row r="936">
+    <row r="936" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P936" s="2"/>
       <c r="S936" s="2"/>
     </row>
-    <row r="937">
+    <row r="937" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P937" s="2"/>
       <c r="S937" s="2"/>
     </row>
-    <row r="938">
+    <row r="938" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P938" s="2"/>
       <c r="S938" s="2"/>
     </row>
-    <row r="939">
+    <row r="939" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P939" s="2"/>
       <c r="S939" s="2"/>
     </row>
-    <row r="940">
+    <row r="940" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P940" s="2"/>
       <c r="S940" s="2"/>
     </row>
-    <row r="941">
+    <row r="941" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P941" s="2"/>
       <c r="S941" s="2"/>
     </row>
-    <row r="942">
+    <row r="942" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P942" s="2"/>
       <c r="S942" s="2"/>
     </row>
-    <row r="943">
+    <row r="943" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P943" s="2"/>
       <c r="S943" s="2"/>
     </row>
-    <row r="944">
+    <row r="944" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P944" s="2"/>
       <c r="S944" s="2"/>
     </row>
-    <row r="945">
+    <row r="945" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P945" s="2"/>
       <c r="S945" s="2"/>
     </row>
-    <row r="946">
+    <row r="946" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P946" s="2"/>
       <c r="S946" s="2"/>
     </row>
-    <row r="947">
+    <row r="947" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P947" s="2"/>
       <c r="S947" s="2"/>
     </row>
-    <row r="948">
+    <row r="948" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P948" s="2"/>
       <c r="S948" s="2"/>
     </row>
-    <row r="949">
+    <row r="949" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P949" s="2"/>
       <c r="S949" s="2"/>
     </row>
-    <row r="950">
+    <row r="950" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P950" s="2"/>
       <c r="S950" s="2"/>
     </row>
-    <row r="951">
+    <row r="951" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P951" s="2"/>
       <c r="S951" s="2"/>
     </row>
-    <row r="952">
+    <row r="952" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P952" s="2"/>
       <c r="S952" s="2"/>
     </row>
-    <row r="953">
+    <row r="953" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P953" s="2"/>
       <c r="S953" s="2"/>
     </row>
-    <row r="954">
+    <row r="954" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P954" s="2"/>
       <c r="S954" s="2"/>
     </row>
-    <row r="955">
+    <row r="955" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P955" s="2"/>
       <c r="S955" s="2"/>
     </row>
-    <row r="956">
+    <row r="956" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P956" s="2"/>
       <c r="S956" s="2"/>
     </row>
-    <row r="957">
+    <row r="957" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P957" s="2"/>
       <c r="S957" s="2"/>
     </row>
-    <row r="958">
+    <row r="958" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P958" s="2"/>
       <c r="S958" s="2"/>
     </row>
-    <row r="959">
+    <row r="959" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P959" s="2"/>
       <c r="S959" s="2"/>
     </row>
-    <row r="960">
+    <row r="960" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P960" s="2"/>
       <c r="S960" s="2"/>
     </row>
-    <row r="961">
+    <row r="961" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P961" s="2"/>
       <c r="S961" s="2"/>
     </row>
-    <row r="962">
+    <row r="962" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P962" s="2"/>
       <c r="S962" s="2"/>
     </row>
-    <row r="963">
+    <row r="963" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P963" s="2"/>
       <c r="S963" s="2"/>
     </row>
-    <row r="964">
+    <row r="964" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P964" s="2"/>
       <c r="S964" s="2"/>
     </row>
-    <row r="965">
+    <row r="965" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P965" s="2"/>
       <c r="S965" s="2"/>
     </row>
-    <row r="966">
+    <row r="966" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P966" s="2"/>
       <c r="S966" s="2"/>
     </row>
-    <row r="967">
+    <row r="967" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P967" s="2"/>
       <c r="S967" s="2"/>
     </row>
-    <row r="968">
+    <row r="968" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P968" s="2"/>
       <c r="S968" s="2"/>
     </row>
-    <row r="969">
+    <row r="969" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P969" s="2"/>
       <c r="S969" s="2"/>
     </row>
-    <row r="970">
+    <row r="970" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P970" s="2"/>
       <c r="S970" s="2"/>
     </row>
-    <row r="971">
+    <row r="971" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P971" s="2"/>
       <c r="S971" s="2"/>
     </row>
-    <row r="972">
+    <row r="972" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P972" s="2"/>
       <c r="S972" s="2"/>
     </row>
-    <row r="973">
+    <row r="973" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P973" s="2"/>
       <c r="S973" s="2"/>
     </row>
-    <row r="974">
+    <row r="974" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P974" s="2"/>
       <c r="S974" s="2"/>
     </row>
-    <row r="975">
+    <row r="975" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P975" s="2"/>
       <c r="S975" s="2"/>
     </row>
-    <row r="976">
+    <row r="976" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P976" s="2"/>
       <c r="S976" s="2"/>
     </row>
-    <row r="977">
+    <row r="977" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P977" s="2"/>
       <c r="S977" s="2"/>
     </row>
-    <row r="978">
+    <row r="978" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P978" s="2"/>
       <c r="S978" s="2"/>
     </row>
-    <row r="979">
+    <row r="979" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P979" s="2"/>
       <c r="S979" s="2"/>
     </row>
-    <row r="980">
+    <row r="980" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P980" s="2"/>
       <c r="S980" s="2"/>
     </row>
-    <row r="981">
+    <row r="981" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P981" s="2"/>
       <c r="S981" s="2"/>
     </row>
-    <row r="982">
+    <row r="982" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P982" s="2"/>
       <c r="S982" s="2"/>
     </row>
-    <row r="983">
+    <row r="983" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P983" s="2"/>
       <c r="S983" s="2"/>
     </row>
-    <row r="984">
+    <row r="984" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P984" s="2"/>
       <c r="S984" s="2"/>
     </row>
-    <row r="985">
+    <row r="985" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P985" s="2"/>
       <c r="S985" s="2"/>
     </row>
-    <row r="986">
+    <row r="986" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P986" s="2"/>
       <c r="S986" s="2"/>
     </row>
-    <row r="987">
+    <row r="987" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P987" s="2"/>
       <c r="S987" s="2"/>
     </row>
-    <row r="988">
+    <row r="988" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P988" s="2"/>
       <c r="S988" s="2"/>
     </row>
-    <row r="989">
+    <row r="989" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P989" s="2"/>
       <c r="S989" s="2"/>
     </row>
-    <row r="990">
+    <row r="990" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P990" s="2"/>
       <c r="S990" s="2"/>
     </row>
-    <row r="991">
+    <row r="991" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P991" s="2"/>
       <c r="S991" s="2"/>
     </row>
-    <row r="992">
+    <row r="992" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P992" s="2"/>
       <c r="S992" s="2"/>
     </row>
-    <row r="993">
+    <row r="993" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P993" s="2"/>
       <c r="S993" s="2"/>
     </row>
-    <row r="994">
+    <row r="994" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P994" s="2"/>
       <c r="S994" s="2"/>
     </row>
-    <row r="995">
+    <row r="995" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P995" s="2"/>
       <c r="S995" s="2"/>
     </row>
-    <row r="996">
+    <row r="996" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P996" s="2"/>
       <c r="S996" s="2"/>
     </row>
-    <row r="997">
+    <row r="997" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P997" s="2"/>
       <c r="S997" s="2"/>
     </row>
-    <row r="998">
+    <row r="998" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P998" s="2"/>
       <c r="S998" s="2"/>
     </row>
-    <row r="999">
+    <row r="999" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P999" s="2"/>
       <c r="S999" s="2"/>
     </row>
-    <row r="1000">
+    <row r="1000" spans="16:19" x14ac:dyDescent="0.2">
       <c r="P1000" s="2"/>
       <c r="S1000" s="2"/>
     </row>
   </sheetData>
-  <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="P1:P1000">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="P1:P1000" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Active,Inactive"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="S1:S1000">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="S1:S1000" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Full time,Part time,Hybrid"</formula1>
     </dataValidation>
   </dataValidations>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/public/sample/users_import.xlsx
+++ b/public/sample/users_import.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pc\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{455BB341-DB38-4F75-AAC4-E416689D631C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26279EDA-5799-4B99-88E2-BEDE4F25C067}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -91,7 +91,7 @@
     <t>Department</t>
   </si>
   <si>
-    <t>reporting_manager_id</t>
+    <t>ReportingManager</t>
   </si>
 </sst>
 </file>

--- a/public/sample/users_import.xlsx
+++ b/public/sample/users_import.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pc\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26279EDA-5799-4B99-88E2-BEDE4F25C067}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A126696C-5129-4D25-AED2-632279F07CDB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,6 +17,40 @@
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
+</file>
+
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Pc</author>
+  </authors>
+  <commentList>
+    <comment ref="P1" authorId="0" shapeId="0" xr:uid="{A6C37592-917F-45B5-91D1-A99E2E7460F1}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Pc:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Please enter employee id of the reporting manager</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -98,7 +132,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -110,6 +144,19 @@
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -350,7 +397,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
@@ -4520,5 +4567,6 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>